--- a/results/TOI-4504 Comparison.xlsx
+++ b/results/TOI-4504 Comparison.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meine Ablage\Python\curvesim\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94866D9B-C282-4290-ADA0-E12D136ABE81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1438D461-6944-45E6-94C2-4B3C4892BF67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="1000" xr2:uid="{6919DDE8-15F9-45FB-B5F7-4209377AF865}"/>
   </bookViews>
@@ -140,7 +140,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="177" formatCode="0.00000"/>
+    <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -222,7 +222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -244,21 +244,17 @@
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -659,7 +655,7 @@
       <c r="E3">
         <v>0.88500000000000001</v>
       </c>
-      <c r="F3" s="20">
+      <c r="F3">
         <v>0.877</v>
       </c>
     </row>
@@ -699,7 +695,7 @@
       <c r="E5">
         <v>2.1278000000000001</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="12">
         <f>F$3*F18*F$33</f>
         <v>2.0212340212017694</v>
       </c>
@@ -720,7 +716,6 @@
       <c r="E6">
         <v>1.012</v>
       </c>
-      <c r="F6" s="20"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -736,7 +731,7 @@
       <c r="E7">
         <v>0.24979999999999999</v>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="12">
         <f>F14*F14+F15*F15</f>
         <v>0.269924</v>
       </c>
@@ -757,7 +752,6 @@
       <c r="E8" s="3">
         <v>91.1</v>
       </c>
-      <c r="F8" s="20"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -775,7 +769,7 @@
       <c r="E9">
         <v>41.787799999999997</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9">
         <v>41.8</v>
       </c>
     </row>
@@ -795,7 +789,6 @@
       <c r="E10">
         <v>0.24</v>
       </c>
-      <c r="F10" s="20"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -814,7 +807,7 @@
       <c r="E11">
         <v>275.8</v>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="13">
         <f>MOD(DEGREES(ATAN2(F15,F14)),360)</f>
         <v>265.58437826536226</v>
       </c>
@@ -855,7 +848,7 @@
       <c r="D13" s="2">
         <v>2458360.8689999999</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F13">
         <v>2458421.7000000002</v>
       </c>
     </row>
@@ -866,7 +859,7 @@
       <c r="B14" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="20">
+      <c r="F14">
         <v>-0.51800000000000002</v>
       </c>
     </row>
@@ -877,7 +870,7 @@
       <c r="B15" t="s">
         <v>23</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15">
         <v>-0.04</v>
       </c>
     </row>
@@ -891,7 +884,6 @@
       <c r="D16">
         <v>-0.24845565999999999</v>
       </c>
-      <c r="F16" s="20"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
@@ -903,7 +895,6 @@
       <c r="D17">
         <v>2.9479829999999999E-2</v>
       </c>
-      <c r="F17" s="20"/>
     </row>
     <row r="18" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
@@ -941,7 +932,7 @@
       <c r="E19">
         <v>2.6315</v>
       </c>
-      <c r="F19" s="21">
+      <c r="F19" s="12">
         <f>F$3*F32*F$33</f>
         <v>2.5908545180859042</v>
       </c>
@@ -962,7 +953,6 @@
       <c r="E20">
         <v>0.98970000000000002</v>
       </c>
-      <c r="F20" s="20"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
@@ -978,7 +968,7 @@
       <c r="E21">
         <v>3.7699999999999997E-2</v>
       </c>
-      <c r="F21" s="21">
+      <c r="F21" s="12">
         <f>F28*F28+F29*F29</f>
         <v>3.8800000000000001E-2</v>
       </c>
@@ -993,13 +983,12 @@
       <c r="C22" t="s">
         <v>22</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="3">
         <v>89.711567000000002</v>
       </c>
       <c r="E22">
         <v>89.69</v>
       </c>
-      <c r="F22" s="20"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
@@ -1017,7 +1006,7 @@
       <c r="E23" s="6">
         <v>81.463099999999997</v>
       </c>
-      <c r="F23" s="20">
+      <c r="F23">
         <v>81.81</v>
       </c>
     </row>
@@ -1037,7 +1026,6 @@
       <c r="E24">
         <v>0.8</v>
       </c>
-      <c r="F24" s="20"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
@@ -1056,7 +1044,7 @@
       <c r="E25" s="1">
         <v>298.89</v>
       </c>
-      <c r="F25" s="22">
+      <c r="F25" s="13">
         <f>MOD(DEGREES(ATAN2(F29,F28)),360)</f>
         <v>293.96248897457815</v>
       </c>
@@ -1096,7 +1084,7 @@
       <c r="D27" s="8">
         <v>2458368.6598</v>
       </c>
-      <c r="F27" s="23">
+      <c r="F27" s="8">
         <v>2458401.3985000001</v>
       </c>
     </row>
@@ -1107,7 +1095,7 @@
       <c r="B28" t="s">
         <v>24</v>
       </c>
-      <c r="F28" s="20">
+      <c r="F28">
         <v>-0.18</v>
       </c>
     </row>
@@ -1118,7 +1106,7 @@
       <c r="B29" t="s">
         <v>23</v>
       </c>
-      <c r="F29" s="20">
+      <c r="F29">
         <v>0.08</v>
       </c>
     </row>
@@ -1135,7 +1123,6 @@
       <c r="E30">
         <v>-2.9159999999999998E-2</v>
       </c>
-      <c r="F30" s="20"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
@@ -1150,7 +1137,6 @@
       <c r="E31">
         <v>1.9390000000000001E-2</v>
       </c>
-      <c r="F31" s="20"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
@@ -1185,7 +1171,7 @@
       <c r="E33">
         <v>1047.5971914594015</v>
       </c>
-      <c r="F33" s="20">
+      <c r="F33">
         <v>1047.5971914594015</v>
       </c>
     </row>

--- a/results/TOI-4504 Comparison.xlsx
+++ b/results/TOI-4504 Comparison.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meine Ablage\Python\curvesim\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1438D461-6944-45E6-94C2-4B3C4892BF67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07023398-8076-4731-8296-943F9DE32DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="1000" xr2:uid="{6919DDE8-15F9-45FB-B5F7-4209377AF865}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="1000" activeTab="1" xr2:uid="{6919DDE8-15F9-45FB-B5F7-4209377AF865}"/>
   </bookViews>
   <sheets>
     <sheet name="Comparison" sheetId="91" r:id="rId1"/>
+    <sheet name="TT" sheetId="92" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="44">
   <si>
     <t>d</t>
   </si>
@@ -130,6 +131,45 @@
   </si>
   <si>
     <t>m Sun / m Jup</t>
+  </si>
+  <si>
+    <t>sector</t>
+  </si>
+  <si>
+    <t>eclipser</t>
+  </si>
+  <si>
+    <t>nr</t>
+  </si>
+  <si>
+    <t>observed</t>
+  </si>
+  <si>
+    <t>observed_err</t>
+  </si>
+  <si>
+    <t>Fast TTV</t>
+  </si>
+  <si>
+    <t>Ø ABS</t>
+  </si>
+  <si>
+    <t>delta std</t>
+  </si>
+  <si>
+    <t>P=81,820097</t>
+  </si>
+  <si>
+    <t>P=81.810665</t>
+  </si>
+  <si>
+    <t>Fast TTV reproduziert die beobachteten TT mit Trifons Bet Fit Parametern sehr gut.</t>
+  </si>
+  <si>
+    <t>Anpassung von P(c) alleine reicht nicht, um mit Uli Best Fit die beobachteten TT zu reproduzieren!</t>
+  </si>
+  <si>
+    <t>P=81.4631</t>
   </si>
 </sst>
 </file>
@@ -142,7 +182,7 @@
     <numFmt numFmtId="166" formatCode="0.0000"/>
     <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -172,16 +212,64 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -218,11 +306,130 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -254,6 +461,113 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -800,14 +1114,14 @@
       <c r="C11" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="20">
         <f>MOD(DEGREES(ATAN2(D17,D16)),360)</f>
         <v>276.76663869301791</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="3">
         <v>275.8</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="20">
         <f>MOD(DEGREES(ATAN2(F15,F14)),360)</f>
         <v>265.58437826536226</v>
       </c>
@@ -822,15 +1136,15 @@
       <c r="C12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="21">
         <f>MOD(DEGREES(((D$2-D13)/D9)*2*PI()),360)</f>
         <v>337.15902078899757</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="22">
         <f>-20.46+360</f>
         <v>339.54</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="21">
         <f>MOD(DEGREES(((F$2-F13)/F9)*2*PI()),360)</f>
         <v>173.11004784528578</v>
       </c>
@@ -1037,7 +1351,7 @@
       <c r="C25" t="s">
         <v>22</v>
       </c>
-      <c r="D25" s="13">
+      <c r="D25" s="20">
         <f>MOD(DEGREES(ATAN2(D31,D30)),360)</f>
         <v>303.62478284868769</v>
       </c>
@@ -1059,7 +1373,7 @@
       <c r="C26" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="21">
         <f>MOD(DEGREES(((D$2-D27)/D23)*2*PI()),360)</f>
         <v>137.89365221593033</v>
       </c>
@@ -1173,6 +1487,884 @@
       </c>
       <c r="F33">
         <v>1047.5971914594015</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F84F1D3-CE28-48A5-9826-1479D22354BC}">
+  <dimension ref="A1:K27"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.140625" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F1" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" s="57">
+        <f>AVERAGE(G4:G23)</f>
+        <v>0.87090304908582861</v>
+      </c>
+      <c r="H1" s="62" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="58">
+        <f>AVERAGE(I4:I23)</f>
+        <v>23.143484979265143</v>
+      </c>
+      <c r="J1" s="62" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" s="58">
+        <f>AVERAGE(K4:K23)</f>
+        <v>715.92776441314822</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="40"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="60" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="52" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="45" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="48" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="61" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="51" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="64" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" s="64" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" s="53" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="23">
+        <v>3</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="25">
+        <v>0</v>
+      </c>
+      <c r="D4" s="26">
+        <v>2458401.4085999997</v>
+      </c>
+      <c r="E4" s="27">
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="F4" s="26">
+        <v>2458401.4106999999</v>
+      </c>
+      <c r="G4" s="54">
+        <f>ABS((F4-D4)/E4)</f>
+        <v>0.65625004936009645</v>
+      </c>
+      <c r="H4" s="26">
+        <v>2458401.4182000002</v>
+      </c>
+      <c r="I4" s="54">
+        <f>ABS((H4-D4)/E4)</f>
+        <v>3.0000001424923539</v>
+      </c>
+      <c r="J4" s="26">
+        <v>2458401.4120999998</v>
+      </c>
+      <c r="K4" s="54">
+        <f>ABS((J4-D4)/E4)</f>
+        <v>1.0937500337604433</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="23">
+        <v>6</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="25">
+        <v>1</v>
+      </c>
+      <c r="D5" s="26">
+        <v>2458483.2110000001</v>
+      </c>
+      <c r="E5" s="27">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="F5" s="26">
+        <v>2458483.2118000002</v>
+      </c>
+      <c r="G5" s="54">
+        <f t="shared" ref="G5:G23" si="0">ABS((F5-D5)/E5)</f>
+        <v>0.23529412882292974</v>
+      </c>
+      <c r="H5" s="26">
+        <v>2458483.2052000002</v>
+      </c>
+      <c r="I5" s="54">
+        <f t="shared" ref="I5:I23" si="1">ABS((H5-D5)/E5)</f>
+        <v>1.705882331246839</v>
+      </c>
+      <c r="J5" s="26">
+        <v>2458482.8635</v>
+      </c>
+      <c r="K5" s="54">
+        <f t="shared" ref="K5:K23" si="2">ABS((J5-D5)/E5)</f>
+        <v>102.20588239676813</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="23">
+        <v>9</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="25">
+        <v>2</v>
+      </c>
+      <c r="D6" s="26">
+        <v>2458565.0902</v>
+      </c>
+      <c r="E6" s="27">
+        <v>3.2499999999999999E-3</v>
+      </c>
+      <c r="F6" s="26">
+        <v>2458565.0959000001</v>
+      </c>
+      <c r="G6" s="54">
+        <f t="shared" si="0"/>
+        <v>1.7538461834192276</v>
+      </c>
+      <c r="H6" s="26">
+        <v>2458565.0822999999</v>
+      </c>
+      <c r="I6" s="54">
+        <f t="shared" si="1"/>
+        <v>2.4307692566743264</v>
+      </c>
+      <c r="J6" s="26">
+        <v>2458564.4419</v>
+      </c>
+      <c r="K6" s="54">
+        <f t="shared" si="2"/>
+        <v>199.47692307715232</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="28">
+        <v>12</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="30">
+        <v>3</v>
+      </c>
+      <c r="D7" s="31">
+        <v>2458647.3328</v>
+      </c>
+      <c r="E7" s="32">
+        <v>4.4000000000000003E-3</v>
+      </c>
+      <c r="F7" s="31">
+        <v>2458647.3298999998</v>
+      </c>
+      <c r="G7" s="55">
+        <f t="shared" si="0"/>
+        <v>0.6590909536250612</v>
+      </c>
+      <c r="H7" s="31">
+        <v>2458647.3202</v>
+      </c>
+      <c r="I7" s="55">
+        <f t="shared" si="1"/>
+        <v>2.8636363673616536</v>
+      </c>
+      <c r="J7" s="31">
+        <v>2458646.4597</v>
+      </c>
+      <c r="K7" s="55">
+        <f t="shared" si="2"/>
+        <v>198.43181817453691</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="23">
+        <v>28</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="25">
+        <v>8</v>
+      </c>
+      <c r="D8" s="26">
+        <v>2459065.2370000002</v>
+      </c>
+      <c r="E8" s="27">
+        <v>2.3500000000000001E-3</v>
+      </c>
+      <c r="F8" s="26">
+        <v>2459065.2407999998</v>
+      </c>
+      <c r="G8" s="54">
+        <f t="shared" si="0"/>
+        <v>1.6170211057079598</v>
+      </c>
+      <c r="H8" s="26">
+        <v>2459065.2357000001</v>
+      </c>
+      <c r="I8" s="54">
+        <f t="shared" si="1"/>
+        <v>0.5531915404061053</v>
+      </c>
+      <c r="J8" s="26">
+        <v>2459064.2108999998</v>
+      </c>
+      <c r="K8" s="54">
+        <f t="shared" si="2"/>
+        <v>436.63829802832703</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="23">
+        <v>31</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="25">
+        <v>9</v>
+      </c>
+      <c r="D9" s="26">
+        <v>2459148.4781999998</v>
+      </c>
+      <c r="E9" s="27">
+        <v>2.65E-3</v>
+      </c>
+      <c r="F9" s="26">
+        <v>2459148.4778999998</v>
+      </c>
+      <c r="G9" s="54">
+        <f t="shared" si="0"/>
+        <v>0.11320753058172622</v>
+      </c>
+      <c r="H9" s="26">
+        <v>2459148.4284999999</v>
+      </c>
+      <c r="I9" s="54">
+        <f t="shared" si="1"/>
+        <v>18.754716927431666</v>
+      </c>
+      <c r="J9" s="26">
+        <v>2459147.1962000001</v>
+      </c>
+      <c r="K9" s="54">
+        <f t="shared" si="2"/>
+        <v>483.77358477632953</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="23">
+        <v>34</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="25">
+        <v>10</v>
+      </c>
+      <c r="D10" s="26">
+        <v>2459231.1144000003</v>
+      </c>
+      <c r="E10" s="27">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="F10" s="26">
+        <v>2459231.1167000001</v>
+      </c>
+      <c r="G10" s="54">
+        <f t="shared" si="0"/>
+        <v>1.0952380086694447</v>
+      </c>
+      <c r="H10" s="26">
+        <v>2459231.0216999999</v>
+      </c>
+      <c r="I10" s="54">
+        <f t="shared" si="1"/>
+        <v>44.142857326992925</v>
+      </c>
+      <c r="J10" s="26">
+        <v>2459229.4999000002</v>
+      </c>
+      <c r="K10" s="54">
+        <f t="shared" si="2"/>
+        <v>768.80952387693389</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="28">
+        <v>37</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="30">
+        <v>11</v>
+      </c>
+      <c r="D11" s="31">
+        <v>2459313.2535000001</v>
+      </c>
+      <c r="E11" s="32">
+        <v>1.9E-3</v>
+      </c>
+      <c r="F11" s="31">
+        <v>2459313.2577999998</v>
+      </c>
+      <c r="G11" s="55">
+        <f t="shared" si="0"/>
+        <v>2.2631577265105749</v>
+      </c>
+      <c r="H11" s="31">
+        <v>2459313.1257000002</v>
+      </c>
+      <c r="I11" s="55">
+        <f t="shared" si="1"/>
+        <v>67.263157842190637</v>
+      </c>
+      <c r="J11" s="31">
+        <v>2459311.2730999999</v>
+      </c>
+      <c r="K11" s="55">
+        <f t="shared" si="2"/>
+        <v>1042.3157895964227</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="23">
+        <v>61</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="25">
+        <v>19</v>
+      </c>
+      <c r="D12" s="26">
+        <v>2459976.0493000001</v>
+      </c>
+      <c r="E12" s="27">
+        <v>4.4000000000000003E-3</v>
+      </c>
+      <c r="F12" s="26">
+        <v>2459976.0480999998</v>
+      </c>
+      <c r="G12" s="54">
+        <f t="shared" si="0"/>
+        <v>0.27272733859717846</v>
+      </c>
+      <c r="H12" s="26">
+        <v>2459976.0643000002</v>
+      </c>
+      <c r="I12" s="54">
+        <f t="shared" si="1"/>
+        <v>3.4090909387238999</v>
+      </c>
+      <c r="J12" s="26">
+        <v>2459973.1538</v>
+      </c>
+      <c r="K12" s="54">
+        <f t="shared" si="2"/>
+        <v>658.06818184104156</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="23">
+        <v>64</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="33">
+        <v>20</v>
+      </c>
+      <c r="D13" s="26">
+        <v>2460059.6189000001</v>
+      </c>
+      <c r="E13" s="27">
+        <v>2.3E-3</v>
+      </c>
+      <c r="F13" s="26">
+        <v>2460059.6168</v>
+      </c>
+      <c r="G13" s="54">
+        <f t="shared" si="0"/>
+        <v>0.91304354693578638</v>
+      </c>
+      <c r="H13" s="26">
+        <v>2460059.5575000001</v>
+      </c>
+      <c r="I13" s="54">
+        <f t="shared" si="1"/>
+        <v>26.695652176504549</v>
+      </c>
+      <c r="J13" s="26">
+        <v>2460056.5010000002</v>
+      </c>
+      <c r="K13" s="54">
+        <f t="shared" si="2"/>
+        <v>1355.6086956320898</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="28">
+        <v>67</v>
+      </c>
+      <c r="B14" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="34">
+        <v>21</v>
+      </c>
+      <c r="D14" s="31">
+        <v>2460142.6048000003</v>
+      </c>
+      <c r="E14" s="32">
+        <v>2.2499999999999998E-3</v>
+      </c>
+      <c r="F14" s="31">
+        <v>2460142.6061</v>
+      </c>
+      <c r="G14" s="55">
+        <f t="shared" si="0"/>
+        <v>0.57777762413024902</v>
+      </c>
+      <c r="H14" s="31">
+        <v>2460142.4610000001</v>
+      </c>
+      <c r="I14" s="55">
+        <f t="shared" si="1"/>
+        <v>63.911111197537849</v>
+      </c>
+      <c r="J14" s="31">
+        <v>2460139.1642999998</v>
+      </c>
+      <c r="K14" s="55">
+        <f t="shared" si="2"/>
+        <v>1529.1111113296615</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="23">
+        <v>89</v>
+      </c>
+      <c r="B15" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="33">
+        <v>28</v>
+      </c>
+      <c r="D15" s="26">
+        <v>2460718.6126000001</v>
+      </c>
+      <c r="E15" s="27">
+        <v>4.5799999999999999E-3</v>
+      </c>
+      <c r="F15" s="26">
+        <v>2460718.6072</v>
+      </c>
+      <c r="G15" s="54">
+        <f t="shared" si="0"/>
+        <v>1.1790393318932129</v>
+      </c>
+      <c r="H15" s="26">
+        <v>2460718.6047</v>
+      </c>
+      <c r="I15" s="54">
+        <f t="shared" si="1"/>
+        <v>1.72489084807676</v>
+      </c>
+      <c r="J15" s="26">
+        <v>2460713.7359000002</v>
+      </c>
+      <c r="K15" s="54">
+        <f t="shared" si="2"/>
+        <v>1064.7816593681491</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="23">
+        <v>95</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="33">
+        <v>30</v>
+      </c>
+      <c r="D16" s="26">
+        <v>2460886.2719999999</v>
+      </c>
+      <c r="E16" s="27">
+        <v>4.5799999999999999E-3</v>
+      </c>
+      <c r="F16" s="26">
+        <v>2460886.2751000002</v>
+      </c>
+      <c r="G16" s="54">
+        <f t="shared" si="0"/>
+        <v>0.67685596547272531</v>
+      </c>
+      <c r="H16" s="26">
+        <v>2460886.3358999998</v>
+      </c>
+      <c r="I16" s="54">
+        <f t="shared" si="1"/>
+        <v>13.951965054602862</v>
+      </c>
+      <c r="J16" s="26">
+        <v>2460881.5249999999</v>
+      </c>
+      <c r="K16" s="54">
+        <f t="shared" si="2"/>
+        <v>1036.4628820903763</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="35">
+        <v>97</v>
+      </c>
+      <c r="B17" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="37">
+        <v>31</v>
+      </c>
+      <c r="D17" s="38">
+        <v>2460970.0865000002</v>
+      </c>
+      <c r="E17" s="39">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="F17" s="38">
+        <v>2460970.0811999999</v>
+      </c>
+      <c r="G17" s="56">
+        <f t="shared" si="0"/>
+        <v>0.88333338499069214</v>
+      </c>
+      <c r="H17" s="38">
+        <v>2460970.0865000002</v>
+      </c>
+      <c r="I17" s="56">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="38">
+        <v>2460965.2303999998</v>
+      </c>
+      <c r="K17" s="56">
+        <f t="shared" si="2"/>
+        <v>809.35000007351243</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="23">
+        <v>88</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="33">
+        <v>0</v>
+      </c>
+      <c r="D18" s="26">
+        <v>2460695.5345999999</v>
+      </c>
+      <c r="E18" s="27">
+        <v>4.5799999999999999E-3</v>
+      </c>
+      <c r="F18" s="26">
+        <v>2460695.5397999999</v>
+      </c>
+      <c r="G18" s="54">
+        <f t="shared" si="0"/>
+        <v>1.1353711821301535</v>
+      </c>
+      <c r="H18" s="26">
+        <v>2460695.3920999998</v>
+      </c>
+      <c r="I18" s="54">
+        <f t="shared" si="1"/>
+        <v>31.113537134171573</v>
+      </c>
+      <c r="J18" s="26">
+        <v>2460691.4147000001</v>
+      </c>
+      <c r="K18" s="54">
+        <f t="shared" si="2"/>
+        <v>899.54148467597611</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="23">
+        <v>89</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="33">
+        <v>1</v>
+      </c>
+      <c r="D19" s="26">
+        <v>2460736.6348999999</v>
+      </c>
+      <c r="E19" s="27">
+        <v>4.5799999999999999E-3</v>
+      </c>
+      <c r="F19" s="26">
+        <v>2460736.6342000002</v>
+      </c>
+      <c r="G19" s="54">
+        <f t="shared" si="0"/>
+        <v>0.1528383716615527</v>
+      </c>
+      <c r="H19" s="26">
+        <v>2460736.4485999998</v>
+      </c>
+      <c r="I19" s="54">
+        <f t="shared" si="1"/>
+        <v>40.676855933588143</v>
+      </c>
+      <c r="J19" s="26">
+        <v>2460732.3349000001</v>
+      </c>
+      <c r="K19" s="54">
+        <f t="shared" si="2"/>
+        <v>938.86462878029158</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="23">
+        <v>94</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="33">
+        <v>4</v>
+      </c>
+      <c r="D20" s="26">
+        <v>2460859.2275</v>
+      </c>
+      <c r="E20" s="27">
+        <v>4.5799999999999999E-3</v>
+      </c>
+      <c r="F20" s="26">
+        <v>2460859.2245</v>
+      </c>
+      <c r="G20" s="54">
+        <f t="shared" si="0"/>
+        <v>0.65502183975481054</v>
+      </c>
+      <c r="H20" s="26">
+        <v>2460858.9695000001</v>
+      </c>
+      <c r="I20" s="54">
+        <f t="shared" si="1"/>
+        <v>56.331877710549854</v>
+      </c>
+      <c r="J20" s="26">
+        <v>2460854.4205</v>
+      </c>
+      <c r="K20" s="54">
+        <f t="shared" si="2"/>
+        <v>1049.5633187837996</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="23">
+        <v>95</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="33">
+        <v>5</v>
+      </c>
+      <c r="D21" s="26">
+        <v>2460900.06</v>
+      </c>
+      <c r="E21" s="27">
+        <v>4.5799999999999999E-3</v>
+      </c>
+      <c r="F21" s="26">
+        <v>2460900.0610000002</v>
+      </c>
+      <c r="G21" s="54">
+        <f t="shared" si="0"/>
+        <v>0.21834064714252688</v>
+      </c>
+      <c r="H21" s="26">
+        <v>2460899.8029999998</v>
+      </c>
+      <c r="I21" s="54">
+        <f t="shared" si="1"/>
+        <v>56.113537165080096</v>
+      </c>
+      <c r="J21" s="26">
+        <v>2460895.1200999999</v>
+      </c>
+      <c r="K21" s="54">
+        <f t="shared" si="2"/>
+        <v>1078.5807860510904</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="23">
+        <v>97</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="33">
+        <v>6</v>
+      </c>
+      <c r="D22" s="26">
+        <v>2460940.8199999998</v>
+      </c>
+      <c r="E22" s="27">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="F22" s="26">
+        <v>2460940.8517</v>
+      </c>
+      <c r="G22" s="54">
+        <f t="shared" si="0"/>
+        <v>0.96060606566342432</v>
+      </c>
+      <c r="H22" s="26">
+        <v>2460940.6022999999</v>
+      </c>
+      <c r="I22" s="54">
+        <f t="shared" si="1"/>
+        <v>6.5969696945764795</v>
+      </c>
+      <c r="J22" s="26">
+        <v>2460935.7941999999</v>
+      </c>
+      <c r="K22" s="54">
+        <f t="shared" si="2"/>
+        <v>152.29696969529894</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="35">
+        <v>97</v>
+      </c>
+      <c r="B23" s="36" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="37">
+        <v>7</v>
+      </c>
+      <c r="D23" s="38">
+        <f>2460981.71</f>
+        <v>2460981.71</v>
+      </c>
+      <c r="E23" s="39">
+        <v>0.01</v>
+      </c>
+      <c r="F23" s="38">
+        <v>2460981.7239999999</v>
+      </c>
+      <c r="G23" s="56">
+        <f t="shared" si="0"/>
+        <v>1.3999999966472387</v>
+      </c>
+      <c r="H23" s="38">
+        <v>2460981.4937</v>
+      </c>
+      <c r="I23" s="56">
+        <f t="shared" si="1"/>
+        <v>21.629999997094274</v>
+      </c>
+      <c r="J23" s="38">
+        <v>2460976.5742000001</v>
+      </c>
+      <c r="K23" s="56">
+        <f t="shared" si="2"/>
+        <v>513.57999998144805</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D26" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/results/TOI-4504 Comparison.xlsx
+++ b/results/TOI-4504 Comparison.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meine Ablage\Python\curvesim\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07023398-8076-4731-8296-943F9DE32DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A265BE55-A389-4489-B978-1B1D13EE2470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="1000" activeTab="1" xr2:uid="{6919DDE8-15F9-45FB-B5F7-4209377AF865}"/>
   </bookViews>
   <sheets>
     <sheet name="Comparison" sheetId="91" r:id="rId1"/>
     <sheet name="TT" sheetId="92" r:id="rId2"/>
+    <sheet name="fuer Hanno Rein" sheetId="93" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="47">
   <si>
     <t>d</t>
   </si>
@@ -170,6 +171,15 @@
   </si>
   <si>
     <t>P=81.4631</t>
+  </si>
+  <si>
+    <t>sim1</t>
+  </si>
+  <si>
+    <t>sim2</t>
+  </si>
+  <si>
+    <t>sim3</t>
   </si>
 </sst>
 </file>
@@ -182,7 +192,7 @@
     <numFmt numFmtId="166" formatCode="0.0000"/>
     <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -229,6 +239,27 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0" tint="-0.14999847407452621"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.14999847407452621"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -429,7 +460,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -516,9 +547,6 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -569,6 +597,24 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1514,24 +1560,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F1" s="59" t="s">
+      <c r="F1" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="57">
+      <c r="G1" s="56">
         <f>AVERAGE(G4:G23)</f>
         <v>0.87090304908582861</v>
       </c>
-      <c r="H1" s="62" t="s">
+      <c r="H1" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="I1" s="58">
+      <c r="I1" s="57">
         <f>AVERAGE(I4:I23)</f>
         <v>23.143484979265143</v>
       </c>
-      <c r="J1" s="62" t="s">
+      <c r="J1" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="K1" s="58">
+      <c r="K1" s="57">
         <f>AVERAGE(K4:K23)</f>
         <v>715.92776441314822</v>
       </c>
@@ -1542,57 +1588,57 @@
       <c r="C2" s="42"/>
       <c r="D2" s="43"/>
       <c r="E2" s="43"/>
-      <c r="F2" s="60" t="s">
+      <c r="F2" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="50" t="s">
+      <c r="G2" s="49" t="s">
         <v>37</v>
       </c>
-      <c r="H2" s="63" t="s">
+      <c r="H2" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="52" t="s">
+      <c r="I2" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="J2" s="63" t="s">
+      <c r="J2" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="52" t="s">
+      <c r="K2" s="51" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="45" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="46" t="s">
+    <row r="3" spans="1:11" s="44" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="47" t="s">
+      <c r="B3" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="48" t="s">
+      <c r="C3" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="D3" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="49" t="s">
+      <c r="E3" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="61" t="s">
+      <c r="F3" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="51" t="s">
+      <c r="G3" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="H3" s="64" t="s">
+      <c r="H3" s="63" t="s">
         <v>36</v>
       </c>
-      <c r="I3" s="53" t="s">
+      <c r="I3" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="64" t="s">
+      <c r="J3" s="63" t="s">
         <v>36</v>
       </c>
-      <c r="K3" s="53" t="s">
+      <c r="K3" s="52" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1615,21 +1661,21 @@
       <c r="F4" s="26">
         <v>2458401.4106999999</v>
       </c>
-      <c r="G4" s="54">
+      <c r="G4" s="53">
         <f>ABS((F4-D4)/E4)</f>
         <v>0.65625004936009645</v>
       </c>
       <c r="H4" s="26">
         <v>2458401.4182000002</v>
       </c>
-      <c r="I4" s="54">
+      <c r="I4" s="53">
         <f>ABS((H4-D4)/E4)</f>
         <v>3.0000001424923539</v>
       </c>
       <c r="J4" s="26">
         <v>2458401.4120999998</v>
       </c>
-      <c r="K4" s="54">
+      <c r="K4" s="53">
         <f>ABS((J4-D4)/E4)</f>
         <v>1.0937500337604433</v>
       </c>
@@ -1653,21 +1699,21 @@
       <c r="F5" s="26">
         <v>2458483.2118000002</v>
       </c>
-      <c r="G5" s="54">
+      <c r="G5" s="53">
         <f t="shared" ref="G5:G23" si="0">ABS((F5-D5)/E5)</f>
         <v>0.23529412882292974</v>
       </c>
       <c r="H5" s="26">
         <v>2458483.2052000002</v>
       </c>
-      <c r="I5" s="54">
+      <c r="I5" s="53">
         <f t="shared" ref="I5:I23" si="1">ABS((H5-D5)/E5)</f>
         <v>1.705882331246839</v>
       </c>
       <c r="J5" s="26">
         <v>2458482.8635</v>
       </c>
-      <c r="K5" s="54">
+      <c r="K5" s="53">
         <f t="shared" ref="K5:K23" si="2">ABS((J5-D5)/E5)</f>
         <v>102.20588239676813</v>
       </c>
@@ -1691,21 +1737,21 @@
       <c r="F6" s="26">
         <v>2458565.0959000001</v>
       </c>
-      <c r="G6" s="54">
+      <c r="G6" s="53">
         <f t="shared" si="0"/>
         <v>1.7538461834192276</v>
       </c>
       <c r="H6" s="26">
         <v>2458565.0822999999</v>
       </c>
-      <c r="I6" s="54">
+      <c r="I6" s="53">
         <f t="shared" si="1"/>
         <v>2.4307692566743264</v>
       </c>
       <c r="J6" s="26">
         <v>2458564.4419</v>
       </c>
-      <c r="K6" s="54">
+      <c r="K6" s="53">
         <f t="shared" si="2"/>
         <v>199.47692307715232</v>
       </c>
@@ -1729,21 +1775,21 @@
       <c r="F7" s="31">
         <v>2458647.3298999998</v>
       </c>
-      <c r="G7" s="55">
+      <c r="G7" s="54">
         <f t="shared" si="0"/>
         <v>0.6590909536250612</v>
       </c>
       <c r="H7" s="31">
         <v>2458647.3202</v>
       </c>
-      <c r="I7" s="55">
+      <c r="I7" s="54">
         <f t="shared" si="1"/>
         <v>2.8636363673616536</v>
       </c>
       <c r="J7" s="31">
         <v>2458646.4597</v>
       </c>
-      <c r="K7" s="55">
+      <c r="K7" s="54">
         <f t="shared" si="2"/>
         <v>198.43181817453691</v>
       </c>
@@ -1767,21 +1813,21 @@
       <c r="F8" s="26">
         <v>2459065.2407999998</v>
       </c>
-      <c r="G8" s="54">
+      <c r="G8" s="53">
         <f t="shared" si="0"/>
         <v>1.6170211057079598</v>
       </c>
       <c r="H8" s="26">
         <v>2459065.2357000001</v>
       </c>
-      <c r="I8" s="54">
+      <c r="I8" s="53">
         <f t="shared" si="1"/>
         <v>0.5531915404061053</v>
       </c>
       <c r="J8" s="26">
         <v>2459064.2108999998</v>
       </c>
-      <c r="K8" s="54">
+      <c r="K8" s="53">
         <f t="shared" si="2"/>
         <v>436.63829802832703</v>
       </c>
@@ -1805,21 +1851,21 @@
       <c r="F9" s="26">
         <v>2459148.4778999998</v>
       </c>
-      <c r="G9" s="54">
+      <c r="G9" s="53">
         <f t="shared" si="0"/>
         <v>0.11320753058172622</v>
       </c>
       <c r="H9" s="26">
         <v>2459148.4284999999</v>
       </c>
-      <c r="I9" s="54">
+      <c r="I9" s="53">
         <f t="shared" si="1"/>
         <v>18.754716927431666</v>
       </c>
       <c r="J9" s="26">
         <v>2459147.1962000001</v>
       </c>
-      <c r="K9" s="54">
+      <c r="K9" s="53">
         <f t="shared" si="2"/>
         <v>483.77358477632953</v>
       </c>
@@ -1843,21 +1889,21 @@
       <c r="F10" s="26">
         <v>2459231.1167000001</v>
       </c>
-      <c r="G10" s="54">
+      <c r="G10" s="53">
         <f t="shared" si="0"/>
         <v>1.0952380086694447</v>
       </c>
       <c r="H10" s="26">
         <v>2459231.0216999999</v>
       </c>
-      <c r="I10" s="54">
+      <c r="I10" s="53">
         <f t="shared" si="1"/>
         <v>44.142857326992925</v>
       </c>
       <c r="J10" s="26">
         <v>2459229.4999000002</v>
       </c>
-      <c r="K10" s="54">
+      <c r="K10" s="53">
         <f t="shared" si="2"/>
         <v>768.80952387693389</v>
       </c>
@@ -1881,21 +1927,21 @@
       <c r="F11" s="31">
         <v>2459313.2577999998</v>
       </c>
-      <c r="G11" s="55">
+      <c r="G11" s="54">
         <f t="shared" si="0"/>
         <v>2.2631577265105749</v>
       </c>
       <c r="H11" s="31">
         <v>2459313.1257000002</v>
       </c>
-      <c r="I11" s="55">
+      <c r="I11" s="54">
         <f t="shared" si="1"/>
         <v>67.263157842190637</v>
       </c>
       <c r="J11" s="31">
         <v>2459311.2730999999</v>
       </c>
-      <c r="K11" s="55">
+      <c r="K11" s="54">
         <f t="shared" si="2"/>
         <v>1042.3157895964227</v>
       </c>
@@ -1919,21 +1965,21 @@
       <c r="F12" s="26">
         <v>2459976.0480999998</v>
       </c>
-      <c r="G12" s="54">
+      <c r="G12" s="53">
         <f t="shared" si="0"/>
         <v>0.27272733859717846</v>
       </c>
       <c r="H12" s="26">
         <v>2459976.0643000002</v>
       </c>
-      <c r="I12" s="54">
+      <c r="I12" s="53">
         <f t="shared" si="1"/>
         <v>3.4090909387238999</v>
       </c>
       <c r="J12" s="26">
         <v>2459973.1538</v>
       </c>
-      <c r="K12" s="54">
+      <c r="K12" s="53">
         <f t="shared" si="2"/>
         <v>658.06818184104156</v>
       </c>
@@ -1957,21 +2003,21 @@
       <c r="F13" s="26">
         <v>2460059.6168</v>
       </c>
-      <c r="G13" s="54">
+      <c r="G13" s="53">
         <f t="shared" si="0"/>
         <v>0.91304354693578638</v>
       </c>
       <c r="H13" s="26">
         <v>2460059.5575000001</v>
       </c>
-      <c r="I13" s="54">
+      <c r="I13" s="53">
         <f t="shared" si="1"/>
         <v>26.695652176504549</v>
       </c>
       <c r="J13" s="26">
         <v>2460056.5010000002</v>
       </c>
-      <c r="K13" s="54">
+      <c r="K13" s="53">
         <f t="shared" si="2"/>
         <v>1355.6086956320898</v>
       </c>
@@ -1995,21 +2041,21 @@
       <c r="F14" s="31">
         <v>2460142.6061</v>
       </c>
-      <c r="G14" s="55">
+      <c r="G14" s="54">
         <f t="shared" si="0"/>
         <v>0.57777762413024902</v>
       </c>
       <c r="H14" s="31">
         <v>2460142.4610000001</v>
       </c>
-      <c r="I14" s="55">
+      <c r="I14" s="54">
         <f t="shared" si="1"/>
         <v>63.911111197537849</v>
       </c>
       <c r="J14" s="31">
         <v>2460139.1642999998</v>
       </c>
-      <c r="K14" s="55">
+      <c r="K14" s="54">
         <f t="shared" si="2"/>
         <v>1529.1111113296615</v>
       </c>
@@ -2033,21 +2079,21 @@
       <c r="F15" s="26">
         <v>2460718.6072</v>
       </c>
-      <c r="G15" s="54">
+      <c r="G15" s="53">
         <f t="shared" si="0"/>
         <v>1.1790393318932129</v>
       </c>
       <c r="H15" s="26">
         <v>2460718.6047</v>
       </c>
-      <c r="I15" s="54">
+      <c r="I15" s="53">
         <f t="shared" si="1"/>
         <v>1.72489084807676</v>
       </c>
       <c r="J15" s="26">
         <v>2460713.7359000002</v>
       </c>
-      <c r="K15" s="54">
+      <c r="K15" s="53">
         <f t="shared" si="2"/>
         <v>1064.7816593681491</v>
       </c>
@@ -2071,21 +2117,21 @@
       <c r="F16" s="26">
         <v>2460886.2751000002</v>
       </c>
-      <c r="G16" s="54">
+      <c r="G16" s="53">
         <f t="shared" si="0"/>
         <v>0.67685596547272531</v>
       </c>
       <c r="H16" s="26">
         <v>2460886.3358999998</v>
       </c>
-      <c r="I16" s="54">
+      <c r="I16" s="53">
         <f t="shared" si="1"/>
         <v>13.951965054602862</v>
       </c>
       <c r="J16" s="26">
         <v>2460881.5249999999</v>
       </c>
-      <c r="K16" s="54">
+      <c r="K16" s="53">
         <f t="shared" si="2"/>
         <v>1036.4628820903763</v>
       </c>
@@ -2109,21 +2155,21 @@
       <c r="F17" s="38">
         <v>2460970.0811999999</v>
       </c>
-      <c r="G17" s="56">
+      <c r="G17" s="55">
         <f t="shared" si="0"/>
         <v>0.88333338499069214</v>
       </c>
       <c r="H17" s="38">
         <v>2460970.0865000002</v>
       </c>
-      <c r="I17" s="56">
+      <c r="I17" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J17" s="38">
         <v>2460965.2303999998</v>
       </c>
-      <c r="K17" s="56">
+      <c r="K17" s="55">
         <f t="shared" si="2"/>
         <v>809.35000007351243</v>
       </c>
@@ -2147,21 +2193,21 @@
       <c r="F18" s="26">
         <v>2460695.5397999999</v>
       </c>
-      <c r="G18" s="54">
+      <c r="G18" s="53">
         <f t="shared" si="0"/>
         <v>1.1353711821301535</v>
       </c>
       <c r="H18" s="26">
         <v>2460695.3920999998</v>
       </c>
-      <c r="I18" s="54">
+      <c r="I18" s="53">
         <f t="shared" si="1"/>
         <v>31.113537134171573</v>
       </c>
       <c r="J18" s="26">
         <v>2460691.4147000001</v>
       </c>
-      <c r="K18" s="54">
+      <c r="K18" s="53">
         <f t="shared" si="2"/>
         <v>899.54148467597611</v>
       </c>
@@ -2185,21 +2231,21 @@
       <c r="F19" s="26">
         <v>2460736.6342000002</v>
       </c>
-      <c r="G19" s="54">
+      <c r="G19" s="53">
         <f t="shared" si="0"/>
         <v>0.1528383716615527</v>
       </c>
       <c r="H19" s="26">
         <v>2460736.4485999998</v>
       </c>
-      <c r="I19" s="54">
+      <c r="I19" s="53">
         <f t="shared" si="1"/>
         <v>40.676855933588143</v>
       </c>
       <c r="J19" s="26">
         <v>2460732.3349000001</v>
       </c>
-      <c r="K19" s="54">
+      <c r="K19" s="53">
         <f t="shared" si="2"/>
         <v>938.86462878029158</v>
       </c>
@@ -2223,21 +2269,21 @@
       <c r="F20" s="26">
         <v>2460859.2245</v>
       </c>
-      <c r="G20" s="54">
+      <c r="G20" s="53">
         <f t="shared" si="0"/>
         <v>0.65502183975481054</v>
       </c>
       <c r="H20" s="26">
         <v>2460858.9695000001</v>
       </c>
-      <c r="I20" s="54">
+      <c r="I20" s="53">
         <f t="shared" si="1"/>
         <v>56.331877710549854</v>
       </c>
       <c r="J20" s="26">
         <v>2460854.4205</v>
       </c>
-      <c r="K20" s="54">
+      <c r="K20" s="53">
         <f t="shared" si="2"/>
         <v>1049.5633187837996</v>
       </c>
@@ -2261,21 +2307,21 @@
       <c r="F21" s="26">
         <v>2460900.0610000002</v>
       </c>
-      <c r="G21" s="54">
+      <c r="G21" s="53">
         <f t="shared" si="0"/>
         <v>0.21834064714252688</v>
       </c>
       <c r="H21" s="26">
         <v>2460899.8029999998</v>
       </c>
-      <c r="I21" s="54">
+      <c r="I21" s="53">
         <f t="shared" si="1"/>
         <v>56.113537165080096</v>
       </c>
       <c r="J21" s="26">
         <v>2460895.1200999999</v>
       </c>
-      <c r="K21" s="54">
+      <c r="K21" s="53">
         <f t="shared" si="2"/>
         <v>1078.5807860510904</v>
       </c>
@@ -2299,21 +2345,21 @@
       <c r="F22" s="26">
         <v>2460940.8517</v>
       </c>
-      <c r="G22" s="54">
+      <c r="G22" s="53">
         <f t="shared" si="0"/>
         <v>0.96060606566342432</v>
       </c>
       <c r="H22" s="26">
         <v>2460940.6022999999</v>
       </c>
-      <c r="I22" s="54">
+      <c r="I22" s="53">
         <f t="shared" si="1"/>
         <v>6.5969696945764795</v>
       </c>
       <c r="J22" s="26">
         <v>2460935.7941999999</v>
       </c>
-      <c r="K22" s="54">
+      <c r="K22" s="53">
         <f t="shared" si="2"/>
         <v>152.29696969529894</v>
       </c>
@@ -2338,21 +2384,21 @@
       <c r="F23" s="38">
         <v>2460981.7239999999</v>
       </c>
-      <c r="G23" s="56">
+      <c r="G23" s="55">
         <f t="shared" si="0"/>
         <v>1.3999999966472387</v>
       </c>
       <c r="H23" s="38">
         <v>2460981.4937</v>
       </c>
-      <c r="I23" s="56">
+      <c r="I23" s="55">
         <f t="shared" si="1"/>
         <v>21.629999997094274</v>
       </c>
       <c r="J23" s="38">
         <v>2460976.5742000001</v>
       </c>
-      <c r="K23" s="56">
+      <c r="K23" s="55">
         <f t="shared" si="2"/>
         <v>513.57999998144805</v>
       </c>
@@ -2365,6 +2411,325 @@
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D27" t="s">
         <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED910461-834B-422D-A228-E4219B5F0CA7}">
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" style="75" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" s="72" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="70" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="70" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="70" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="71">
+        <v>0.88500000000000001</v>
+      </c>
+      <c r="E2" s="71">
+        <v>0.88500000000000001</v>
+      </c>
+      <c r="F2" s="73">
+        <v>0.877</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="64">
+        <v>2.1278000000000001</v>
+      </c>
+      <c r="E3" s="64">
+        <v>2.1511999999999998</v>
+      </c>
+      <c r="F3" s="74">
+        <v>2.0212340212017694</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="64">
+        <v>0.24979999999999999</v>
+      </c>
+      <c r="E4" s="65">
+        <v>0.25019847194350425</v>
+      </c>
+      <c r="F4" s="74">
+        <v>0.269924</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="66">
+        <v>91.1</v>
+      </c>
+      <c r="E5" s="66">
+        <v>88.763733999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="64">
+        <v>41.787799999999997</v>
+      </c>
+      <c r="E6" s="65">
+        <v>41.781945999999998</v>
+      </c>
+      <c r="F6" s="75">
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="64">
+        <v>0.24</v>
+      </c>
+      <c r="E7" s="64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="66">
+        <v>275.8</v>
+      </c>
+      <c r="E8" s="66">
+        <v>276.76663869301791</v>
+      </c>
+      <c r="F8" s="76">
+        <v>265.58437826536226</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="67">
+        <v>339.54</v>
+      </c>
+      <c r="E9" s="67">
+        <v>337.15902078899757</v>
+      </c>
+      <c r="F9" s="77">
+        <v>173.11004784528578</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="64">
+        <v>2.6315</v>
+      </c>
+      <c r="E10" s="65">
+        <v>2.63849</v>
+      </c>
+      <c r="F10" s="74">
+        <v>2.5908545180859042</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="64">
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="E11" s="65">
+        <v>3.5024375561053193E-2</v>
+      </c>
+      <c r="F11" s="74">
+        <v>3.8800000000000001E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="64">
+        <v>89.69</v>
+      </c>
+      <c r="E12" s="66">
+        <v>89.711567000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="6">
+        <v>81.463099999999997</v>
+      </c>
+      <c r="E13" s="64">
+        <v>81.820097000000004</v>
+      </c>
+      <c r="F13" s="75">
+        <v>81.81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="64">
+        <v>0.8</v>
+      </c>
+      <c r="E14" s="64">
+        <v>-2.016956</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="68">
+        <v>298.89</v>
+      </c>
+      <c r="E15" s="66">
+        <v>303.62478284868769</v>
+      </c>
+      <c r="F15" s="78">
+        <v>293.96248897457815</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="69">
+        <v>142.72</v>
+      </c>
+      <c r="E16" s="67">
+        <v>137.89365221593033</v>
+      </c>
+      <c r="F16" s="79">
+        <v>353.84598459790249</v>
       </c>
     </row>
   </sheetData>

--- a/results/TOI-4504 Comparison.xlsx
+++ b/results/TOI-4504 Comparison.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meine Ablage\Python\curvesim\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A265BE55-A389-4489-B978-1B1D13EE2470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{227C2EA6-98A8-4CFE-9A06-BC5AB2C53925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="1000" activeTab="1" xr2:uid="{6919DDE8-15F9-45FB-B5F7-4209377AF865}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="1000" xr2:uid="{6919DDE8-15F9-45FB-B5F7-4209377AF865}"/>
   </bookViews>
   <sheets>
     <sheet name="Comparison" sheetId="91" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="46">
   <si>
     <t>d</t>
   </si>
@@ -177,9 +177,6 @@
   </si>
   <si>
     <t>sim2</t>
-  </si>
-  <si>
-    <t>sim3</t>
   </si>
 </sst>
 </file>
@@ -192,7 +189,7 @@
     <numFmt numFmtId="166" formatCode="0.0000"/>
     <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -242,21 +239,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0" tint="-0.14999847407452621"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0" tint="-0.14999847407452621"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -460,7 +442,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -605,16 +587,6 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1543,7 +1515,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F84F1D3-CE28-48A5-9826-1479D22354BC}">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.42578125" bestFit="1" customWidth="1"/>
@@ -1559,7 +1531,7 @@
     <col min="11" max="11" width="9.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F1" s="58" t="s">
         <v>39</v>
       </c>
@@ -1582,7 +1554,7 @@
         <v>715.92776441314822</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40"/>
       <c r="B2" s="41"/>
       <c r="C2" s="42"/>
@@ -1607,7 +1579,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="44" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" s="44" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="45" t="s">
         <v>31</v>
       </c>
@@ -1642,7 +1614,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="23">
         <v>3</v>
       </c>
@@ -1680,7 +1652,7 @@
         <v>1.0937500337604433</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="23">
         <v>6</v>
       </c>
@@ -1717,8 +1689,9 @@
         <f t="shared" ref="K5:K23" si="2">ABS((J5-D5)/E5)</f>
         <v>102.20588239676813</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M5" s="8"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="23">
         <v>9</v>
       </c>
@@ -1755,8 +1728,9 @@
         <f t="shared" si="2"/>
         <v>199.47692307715232</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M6" s="8"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="28">
         <v>12</v>
       </c>
@@ -1793,8 +1767,9 @@
         <f t="shared" si="2"/>
         <v>198.43181817453691</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M7" s="8"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="23">
         <v>28</v>
       </c>
@@ -1831,8 +1806,9 @@
         <f t="shared" si="2"/>
         <v>436.63829802832703</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M8" s="8"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="23">
         <v>31</v>
       </c>
@@ -1869,8 +1845,9 @@
         <f t="shared" si="2"/>
         <v>483.77358477632953</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M9" s="8"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="23">
         <v>34</v>
       </c>
@@ -1907,8 +1884,9 @@
         <f t="shared" si="2"/>
         <v>768.80952387693389</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M10" s="8"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="28">
         <v>37</v>
       </c>
@@ -1945,8 +1923,9 @@
         <f t="shared" si="2"/>
         <v>1042.3157895964227</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M11" s="8"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="23">
         <v>61</v>
       </c>
@@ -1983,8 +1962,9 @@
         <f t="shared" si="2"/>
         <v>658.06818184104156</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M12" s="8"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="23">
         <v>64</v>
       </c>
@@ -2021,8 +2001,9 @@
         <f t="shared" si="2"/>
         <v>1355.6086956320898</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M13" s="8"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="28">
         <v>67</v>
       </c>
@@ -2059,8 +2040,9 @@
         <f t="shared" si="2"/>
         <v>1529.1111113296615</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M14" s="8"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="23">
         <v>89</v>
       </c>
@@ -2097,8 +2079,9 @@
         <f t="shared" si="2"/>
         <v>1064.7816593681491</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M15" s="8"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="23">
         <v>95</v>
       </c>
@@ -2135,8 +2118,9 @@
         <f t="shared" si="2"/>
         <v>1036.4628820903763</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M16" s="8"/>
+    </row>
+    <row r="17" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="35">
         <v>97</v>
       </c>
@@ -2173,8 +2157,9 @@
         <f t="shared" si="2"/>
         <v>809.35000007351243</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M17" s="8"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="23">
         <v>88</v>
       </c>
@@ -2211,8 +2196,9 @@
         <f t="shared" si="2"/>
         <v>899.54148467597611</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M18" s="8"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="23">
         <v>89</v>
       </c>
@@ -2249,8 +2235,9 @@
         <f t="shared" si="2"/>
         <v>938.86462878029158</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M19" s="8"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="23">
         <v>94</v>
       </c>
@@ -2287,8 +2274,9 @@
         <f t="shared" si="2"/>
         <v>1049.5633187837996</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M20" s="8"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="23">
         <v>95</v>
       </c>
@@ -2325,8 +2313,9 @@
         <f t="shared" si="2"/>
         <v>1078.5807860510904</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M21" s="8"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="23">
         <v>97</v>
       </c>
@@ -2363,8 +2352,9 @@
         <f t="shared" si="2"/>
         <v>152.29696969529894</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="35">
         <v>97</v>
       </c>
@@ -2402,13 +2392,20 @@
         <f t="shared" si="2"/>
         <v>513.57999998144805</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M23" s="8"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M24" s="8"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M25" s="8"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D26" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D27" t="s">
         <v>42</v>
       </c>
@@ -2421,16 +2418,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED910461-834B-422D-A228-E4219B5F0CA7}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>13</v>
       </c>
@@ -2446,11 +2442,8 @@
       <c r="E1" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="72" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="70" t="s">
         <v>6</v>
       </c>
@@ -2466,11 +2459,8 @@
       <c r="E2" s="71">
         <v>0.88500000000000001</v>
       </c>
-      <c r="F2" s="73">
-        <v>0.877</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -2486,11 +2476,8 @@
       <c r="E3" s="64">
         <v>2.1511999999999998</v>
       </c>
-      <c r="F3" s="74">
-        <v>2.0212340212017694</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -2503,11 +2490,8 @@
       <c r="E4" s="65">
         <v>0.25019847194350425</v>
       </c>
-      <c r="F4" s="74">
-        <v>0.269924</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -2524,7 +2508,7 @@
         <v>88.763733999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -2540,11 +2524,8 @@
       <c r="E6" s="65">
         <v>41.781945999999998</v>
       </c>
-      <c r="F6" s="75">
-        <v>41.8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -2561,7 +2542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -2577,11 +2558,8 @@
       <c r="E8" s="66">
         <v>276.76663869301791</v>
       </c>
-      <c r="F8" s="76">
-        <v>265.58437826536226</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>7</v>
       </c>
@@ -2597,11 +2575,8 @@
       <c r="E9" s="67">
         <v>337.15902078899757</v>
       </c>
-      <c r="F9" s="77">
-        <v>173.11004784528578</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -2617,11 +2592,8 @@
       <c r="E10" s="65">
         <v>2.63849</v>
       </c>
-      <c r="F10" s="74">
-        <v>2.5908545180859042</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -2634,11 +2606,8 @@
       <c r="E11" s="65">
         <v>3.5024375561053193E-2</v>
       </c>
-      <c r="F11" s="74">
-        <v>3.8800000000000001E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -2655,7 +2624,7 @@
         <v>89.711567000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -2671,11 +2640,8 @@
       <c r="E13" s="64">
         <v>81.820097000000004</v>
       </c>
-      <c r="F13" s="75">
-        <v>81.81</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -2692,7 +2658,7 @@
         <v>-2.016956</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -2708,11 +2674,8 @@
       <c r="E15" s="66">
         <v>303.62478284868769</v>
       </c>
-      <c r="F15" s="78">
-        <v>293.96248897457815</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>10</v>
       </c>
@@ -2727,9 +2690,6 @@
       </c>
       <c r="E16" s="67">
         <v>137.89365221593033</v>
-      </c>
-      <c r="F16" s="79">
-        <v>353.84598459790249</v>
       </c>
     </row>
   </sheetData>

--- a/results/TOI-4504 Comparison.xlsx
+++ b/results/TOI-4504 Comparison.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meine Ablage\Python\curvesim\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{227C2EA6-98A8-4CFE-9A06-BC5AB2C53925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C465C7-E1D0-4CA5-A960-E424E4FCB35D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="1000" xr2:uid="{6919DDE8-15F9-45FB-B5F7-4209377AF865}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="48">
   <si>
     <t>d</t>
   </si>
@@ -177,6 +177,12 @@
   </si>
   <si>
     <t>sim2</t>
+  </si>
+  <si>
+    <t>Uli true</t>
+  </si>
+  <si>
+    <t>Uli false</t>
   </si>
 </sst>
 </file>
@@ -189,7 +195,7 @@
     <numFmt numFmtId="166" formatCode="0.0000"/>
     <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -239,6 +245,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -442,7 +455,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -587,6 +600,7 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -926,16 +940,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CBA9F35-6018-400E-B5CC-CA22C216F82B}">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>13</v>
       </c>
@@ -949,13 +963,16 @@
         <v>16</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>2</v>
       </c>
@@ -967,11 +984,14 @@
       <c r="E2" s="16">
         <v>2458400</v>
       </c>
-      <c r="F2" s="19">
+      <c r="F2" s="16">
         <v>2458400</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" s="19">
+        <v>2458400</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -988,10 +1008,13 @@
         <v>0.88500000000000001</v>
       </c>
       <c r="F3">
+        <v>0.88500000000000001</v>
+      </c>
+      <c r="G3">
         <v>0.877</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -1008,10 +1031,13 @@
         <v>0.92</v>
       </c>
       <c r="F4" s="4">
+        <v>0.92</v>
+      </c>
+      <c r="G4" s="4">
         <v>0.93100000000000005</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1027,12 +1053,15 @@
       <c r="E5">
         <v>2.1278000000000001</v>
       </c>
-      <c r="F5" s="12">
-        <f>F$3*F18*F$33</f>
+      <c r="F5">
+        <v>2.1278000000000001</v>
+      </c>
+      <c r="G5" s="12">
+        <f>G$3*G18*G$33</f>
         <v>2.0212340212017694</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1048,8 +1077,11 @@
       <c r="E6">
         <v>1.012</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F6">
+        <v>1.012</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1063,12 +1095,15 @@
       <c r="E7">
         <v>0.24979999999999999</v>
       </c>
-      <c r="F7" s="12">
-        <f>F14*F14+F15*F15</f>
+      <c r="F7">
+        <v>0.24979999999999999</v>
+      </c>
+      <c r="G7" s="12">
+        <f>G14*G14+G15*G15</f>
         <v>0.269924</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1084,8 +1119,11 @@
       <c r="E8" s="3">
         <v>91.1</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F8" s="3">
+        <v>91.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1102,10 +1140,13 @@
         <v>41.787799999999997</v>
       </c>
       <c r="F9">
+        <v>41.787799999999997</v>
+      </c>
+      <c r="G9">
         <v>41.8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -1121,8 +1162,11 @@
       <c r="E10">
         <v>0.24</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F10">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -1139,12 +1183,15 @@
       <c r="E11" s="3">
         <v>275.8</v>
       </c>
-      <c r="F11" s="20">
-        <f>MOD(DEGREES(ATAN2(F15,F14)),360)</f>
+      <c r="F11" s="3">
+        <v>275.8</v>
+      </c>
+      <c r="G11" s="20">
+        <f>MOD(DEGREES(ATAN2(G15,G14)),360)</f>
         <v>265.58437826536226</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>7</v>
       </c>
@@ -1162,12 +1209,16 @@
         <f>-20.46+360</f>
         <v>339.54</v>
       </c>
-      <c r="F12" s="21">
-        <f>MOD(DEGREES(((F$2-F13)/F9)*2*PI()),360)</f>
+      <c r="F12" s="22">
+        <f>-20.46+360</f>
+        <v>339.54</v>
+      </c>
+      <c r="G12" s="21">
+        <f>MOD(DEGREES(((G$2-G13)/G9)*2*PI()),360)</f>
         <v>173.11004784528578</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -1180,33 +1231,33 @@
       <c r="D13" s="2">
         <v>2458360.8689999999</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>2458421.7000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>7</v>
       </c>
       <c r="B14" t="s">
         <v>24</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>-0.51800000000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>7</v>
       </c>
       <c r="B15" t="s">
         <v>23</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>-0.04</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -1217,7 +1268,7 @@
         <v>-0.24845565999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -1228,7 +1279,7 @@
         <v>2.9479829999999999E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>7</v>
       </c>
@@ -1245,10 +1296,14 @@
         <v>2.2950555852114564E-3</v>
       </c>
       <c r="F18" s="15">
+        <f>F5/F$3/F$33</f>
+        <v>2.2950555852114564E-3</v>
+      </c>
+      <c r="G18" s="15">
         <v>2.2000000000000001E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>10</v>
       </c>
@@ -1264,12 +1319,15 @@
       <c r="E19">
         <v>2.6315</v>
       </c>
-      <c r="F19" s="12">
-        <f>F$3*F32*F$33</f>
+      <c r="F19">
+        <v>2.6315</v>
+      </c>
+      <c r="G19" s="12">
+        <f>G$3*G32*G$33</f>
         <v>2.5908545180859042</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1285,8 +1343,11 @@
       <c r="E20">
         <v>0.98970000000000002</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F20">
+        <v>0.98970000000000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -1298,14 +1359,17 @@
         <v>3.5024375561053193E-2</v>
       </c>
       <c r="E21">
+        <v>3.5924999999999999E-2</v>
+      </c>
+      <c r="F21">
         <v>3.7699999999999997E-2</v>
       </c>
-      <c r="F21" s="12">
-        <f>F28*F28+F29*F29</f>
+      <c r="G21" s="12">
+        <f>G28*G28+G29*G29</f>
         <v>3.8800000000000001E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -1321,8 +1385,11 @@
       <c r="E22">
         <v>89.69</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F22">
+        <v>89.69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -1335,14 +1402,17 @@
       <c r="D23">
         <v>81.820097000000004</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="72">
+        <v>81.821389999999994</v>
+      </c>
+      <c r="F23" s="6">
         <v>81.463099999999997</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>81.81</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>10</v>
       </c>
@@ -1358,8 +1428,11 @@
       <c r="E24">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F24">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>10</v>
       </c>
@@ -1374,14 +1447,17 @@
         <v>303.62478284868769</v>
       </c>
       <c r="E25" s="1">
+        <v>300.97730300000001</v>
+      </c>
+      <c r="F25" s="1">
         <v>298.89</v>
       </c>
-      <c r="F25" s="13">
-        <f>MOD(DEGREES(ATAN2(F29,F28)),360)</f>
+      <c r="G25" s="13">
+        <f>MOD(DEGREES(ATAN2(G29,G28)),360)</f>
         <v>293.96248897457815</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>10</v>
       </c>
@@ -1396,14 +1472,17 @@
         <v>137.89365221593033</v>
       </c>
       <c r="E26" s="9">
+        <v>140.63120000000001</v>
+      </c>
+      <c r="F26" s="9">
         <v>142.72</v>
       </c>
-      <c r="F26" s="14">
-        <f>MOD(DEGREES(((F$2-F27)/F23)*2*PI()),360)</f>
+      <c r="G26" s="14">
+        <f>MOD(DEGREES(((G$2-G27)/G23)*2*PI()),360)</f>
         <v>353.84598459790249</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>10</v>
       </c>
@@ -1416,33 +1495,33 @@
       <c r="D27" s="8">
         <v>2458368.6598</v>
       </c>
-      <c r="F27" s="8">
+      <c r="G27" s="8">
         <v>2458401.3985000001</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>10</v>
       </c>
       <c r="B28" t="s">
         <v>24</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>-0.18</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>10</v>
       </c>
       <c r="B29" t="s">
         <v>23</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <v>0.08</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>10</v>
       </c>
@@ -1452,11 +1531,8 @@
       <c r="D30">
         <v>-2.9164160000000001E-2</v>
       </c>
-      <c r="E30">
-        <v>-2.9159999999999998E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>10</v>
       </c>
@@ -1466,11 +1542,8 @@
       <c r="D31">
         <v>1.9394809999999998E-2</v>
       </c>
-      <c r="E31">
-        <v>1.9390000000000001E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>10</v>
       </c>
@@ -1486,11 +1559,15 @@
         <f>E19/E$3/E$33</f>
         <v>2.8383488920405799E-3</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F32" s="18">
+        <f>F19/F$3/F$33</f>
+        <v>2.8383488920405799E-3</v>
+      </c>
+      <c r="G32" s="4">
         <v>2.82E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>30</v>
       </c>
@@ -1504,6 +1581,9 @@
         <v>1047.5971914594015</v>
       </c>
       <c r="F33">
+        <v>1047.5971914594015</v>
+      </c>
+      <c r="G33">
         <v>1047.5971914594015</v>
       </c>
     </row>

--- a/results/TOI-4504 Comparison.xlsx
+++ b/results/TOI-4504 Comparison.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meine Ablage\Python\curvesim\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C465C7-E1D0-4CA5-A960-E424E4FCB35D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4E68342-238C-4AAC-80F8-0E6405423D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="1000" xr2:uid="{6919DDE8-15F9-45FB-B5F7-4209377AF865}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="50">
   <si>
     <t>d</t>
   </si>
@@ -179,10 +179,19 @@
     <t>sim2</t>
   </si>
   <si>
-    <t>Uli true</t>
-  </si>
-  <si>
-    <t>Uli false</t>
+    <t>Michaela
+Trifon</t>
+  </si>
+  <si>
+    <t>Uli
+jacobimasses =true</t>
+  </si>
+  <si>
+    <t>Uli
+jacobimasses =false</t>
+  </si>
+  <si>
+    <t>chi_squared_tt</t>
   </si>
 </sst>
 </file>
@@ -195,7 +204,7 @@
     <numFmt numFmtId="166" formatCode="0.0000"/>
     <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -252,6 +261,21 @@
     <font>
       <sz val="11"/>
       <color rgb="FF00B050"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.499984740745262"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -455,7 +479,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -476,7 +500,6 @@
     </xf>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -601,6 +624,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -940,16 +979,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CBA9F35-6018-400E-B5CC-CA22C216F82B}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.85546875" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="76" customWidth="1"/>
+    <col min="7" max="7" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>13</v>
       </c>
@@ -959,35 +999,35 @@
       <c r="C1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="11" t="s">
+      <c r="D1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="E1" s="7" t="s">
         <v>47</v>
+      </c>
+      <c r="F1" s="74" t="s">
+        <v>48</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="16">
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="15">
         <v>2458400</v>
       </c>
-      <c r="E2" s="16">
+      <c r="E2" s="15">
         <v>2458400</v>
       </c>
-      <c r="F2" s="16">
+      <c r="F2" s="75">
         <v>2458400</v>
       </c>
-      <c r="G2" s="19">
+      <c r="G2" s="18">
         <v>2458400</v>
       </c>
     </row>
@@ -1007,7 +1047,7 @@
       <c r="E3">
         <v>0.88500000000000001</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="76">
         <v>0.88500000000000001</v>
       </c>
       <c r="G3">
@@ -1030,7 +1070,7 @@
       <c r="E4" s="4">
         <v>0.92</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="77">
         <v>0.92</v>
       </c>
       <c r="G4" s="4">
@@ -1053,7 +1093,7 @@
       <c r="E5">
         <v>2.1278000000000001</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="76">
         <v>2.1278000000000001</v>
       </c>
       <c r="G5" s="12">
@@ -1077,7 +1117,7 @@
       <c r="E6">
         <v>1.012</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="76">
         <v>1.012</v>
       </c>
     </row>
@@ -1095,7 +1135,7 @@
       <c r="E7">
         <v>0.24979999999999999</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="76">
         <v>0.24979999999999999</v>
       </c>
       <c r="G7" s="12">
@@ -1119,7 +1159,7 @@
       <c r="E8" s="3">
         <v>91.1</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="78">
         <v>91.1</v>
       </c>
     </row>
@@ -1139,7 +1179,7 @@
       <c r="E9">
         <v>41.787799999999997</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="76">
         <v>41.787799999999997</v>
       </c>
       <c r="G9">
@@ -1162,7 +1202,7 @@
       <c r="E10">
         <v>0.24</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="76">
         <v>0.24</v>
       </c>
     </row>
@@ -1176,17 +1216,17 @@
       <c r="C11" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="19">
         <f>MOD(DEGREES(ATAN2(D17,D16)),360)</f>
         <v>276.76663869301791</v>
       </c>
       <c r="E11" s="3">
         <v>275.8</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="78">
         <v>275.8</v>
       </c>
-      <c r="G11" s="20">
+      <c r="G11" s="19">
         <f>MOD(DEGREES(ATAN2(G15,G14)),360)</f>
         <v>265.58437826536226</v>
       </c>
@@ -1201,19 +1241,19 @@
       <c r="C12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="20">
         <f>MOD(DEGREES(((D$2-D13)/D9)*2*PI()),360)</f>
         <v>337.15902078899757</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="21">
         <f>-20.46+360</f>
         <v>339.54</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="79">
         <f>-20.46+360</f>
         <v>339.54</v>
       </c>
-      <c r="G12" s="21">
+      <c r="G12" s="73">
         <f>MOD(DEGREES(((G$2-G13)/G9)*2*PI()),360)</f>
         <v>173.11004784528578</v>
       </c>
@@ -1287,19 +1327,19 @@
         <v>25</v>
       </c>
       <c r="C18" s="5"/>
-      <c r="D18" s="15">
+      <c r="D18" s="14">
         <f>D5/D$3/D$33</f>
         <v>2.3202949407401465E-3</v>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="14">
         <f>E5/E$3/E$33</f>
         <v>2.2950555852114564E-3</v>
       </c>
-      <c r="F18" s="15">
+      <c r="F18" s="80">
         <f>F5/F$3/F$33</f>
         <v>2.2950555852114564E-3</v>
       </c>
-      <c r="G18" s="15">
+      <c r="G18" s="14">
         <v>2.2000000000000001E-3</v>
       </c>
     </row>
@@ -1319,7 +1359,7 @@
       <c r="E19">
         <v>2.6315</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="76">
         <v>2.6315</v>
       </c>
       <c r="G19" s="12">
@@ -1343,7 +1383,7 @@
       <c r="E20">
         <v>0.98970000000000002</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="76">
         <v>0.98970000000000002</v>
       </c>
     </row>
@@ -1358,10 +1398,10 @@
         <f>SQRT(D30*D30+D31*D31)</f>
         <v>3.5024375561053193E-2</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="8">
         <v>3.5924999999999999E-2</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="76">
         <v>3.7699999999999997E-2</v>
       </c>
       <c r="G21" s="12">
@@ -1385,7 +1425,7 @@
       <c r="E22">
         <v>89.69</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="76">
         <v>89.69</v>
       </c>
     </row>
@@ -1402,10 +1442,10 @@
       <c r="D23">
         <v>81.820097000000004</v>
       </c>
-      <c r="E23" s="72">
+      <c r="E23" s="71">
         <v>81.821389999999994</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="76">
         <v>81.463099999999997</v>
       </c>
       <c r="G23">
@@ -1428,7 +1468,7 @@
       <c r="E24">
         <v>0.8</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="76">
         <v>0.8</v>
       </c>
     </row>
@@ -1442,14 +1482,14 @@
       <c r="C25" t="s">
         <v>22</v>
       </c>
-      <c r="D25" s="20">
+      <c r="D25" s="19">
         <f>MOD(DEGREES(ATAN2(D31,D30)),360)</f>
         <v>303.62478284868769</v>
       </c>
       <c r="E25" s="1">
         <v>300.97730300000001</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F25" s="81">
         <v>298.89</v>
       </c>
       <c r="G25" s="13">
@@ -1467,17 +1507,17 @@
       <c r="C26" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D26" s="21">
+      <c r="D26" s="20">
         <f>MOD(DEGREES(((D$2-D27)/D23)*2*PI()),360)</f>
         <v>137.89365221593033</v>
       </c>
       <c r="E26" s="9">
         <v>140.63120000000001</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F26" s="82">
         <v>142.72</v>
       </c>
-      <c r="G26" s="14">
+      <c r="G26" s="72">
         <f>MOD(DEGREES(((G$2-G27)/G23)*2*PI()),360)</f>
         <v>353.84598459790249</v>
       </c>
@@ -1551,15 +1591,15 @@
         <v>25</v>
       </c>
       <c r="C32" s="4"/>
-      <c r="D32" s="18">
+      <c r="D32" s="17">
         <f>D19/D$3/D$33</f>
         <v>2.8458883405510739E-3</v>
       </c>
-      <c r="E32" s="18">
+      <c r="E32" s="17">
         <f>E19/E$3/E$33</f>
         <v>2.8383488920405799E-3</v>
       </c>
-      <c r="F32" s="18">
+      <c r="F32" s="83">
         <f>F19/F$3/F$33</f>
         <v>2.8383488920405799E-3</v>
       </c>
@@ -1580,11 +1620,19 @@
       <c r="E33">
         <v>1047.5971914594015</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="76">
         <v>1047.5971914594015</v>
       </c>
       <c r="G33">
         <v>1047.5971914594015</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" s="63" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>49</v>
+      </c>
+      <c r="E34" s="63">
+        <v>25.03</v>
       </c>
     </row>
   </sheetData>
@@ -1612,863 +1660,863 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F1" s="58" t="s">
+      <c r="F1" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="56">
+      <c r="G1" s="55">
         <f>AVERAGE(G4:G23)</f>
         <v>0.87090304908582861</v>
       </c>
-      <c r="H1" s="61" t="s">
+      <c r="H1" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="I1" s="57">
+      <c r="I1" s="56">
         <f>AVERAGE(I4:I23)</f>
         <v>23.143484979265143</v>
       </c>
-      <c r="J1" s="61" t="s">
+      <c r="J1" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="K1" s="57">
+      <c r="K1" s="56">
         <f>AVERAGE(K4:K23)</f>
         <v>715.92776441314822</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="44" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="40"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="59" t="s">
+    <row r="2" spans="1:13" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="39"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="49" t="s">
+      <c r="G2" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="H2" s="62" t="s">
+      <c r="H2" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="51" t="s">
+      <c r="I2" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="J2" s="62" t="s">
+      <c r="J2" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="51" t="s">
+      <c r="K2" s="50" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="44" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="45" t="s">
+    <row r="3" spans="1:13" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="47" t="s">
+      <c r="C3" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="48" t="s">
+      <c r="D3" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="48" t="s">
+      <c r="E3" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="60" t="s">
+      <c r="F3" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="50" t="s">
+      <c r="G3" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="H3" s="63" t="s">
+      <c r="H3" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="I3" s="52" t="s">
+      <c r="I3" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="63" t="s">
+      <c r="J3" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="K3" s="52" t="s">
+      <c r="K3" s="51" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="23">
+      <c r="A4" s="22">
         <v>3</v>
       </c>
-      <c r="B4" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="25">
+      <c r="B4" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="24">
         <v>0</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="25">
         <v>2458401.4085999997</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="26">
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="25">
         <v>2458401.4106999999</v>
       </c>
-      <c r="G4" s="53">
+      <c r="G4" s="52">
         <f>ABS((F4-D4)/E4)</f>
         <v>0.65625004936009645</v>
       </c>
-      <c r="H4" s="26">
+      <c r="H4" s="25">
         <v>2458401.4182000002</v>
       </c>
-      <c r="I4" s="53">
+      <c r="I4" s="52">
         <f>ABS((H4-D4)/E4)</f>
         <v>3.0000001424923539</v>
       </c>
-      <c r="J4" s="26">
+      <c r="J4" s="25">
         <v>2458401.4120999998</v>
       </c>
-      <c r="K4" s="53">
+      <c r="K4" s="52">
         <f>ABS((J4-D4)/E4)</f>
         <v>1.0937500337604433</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="23">
+      <c r="A5" s="22">
         <v>6</v>
       </c>
-      <c r="B5" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="25">
+      <c r="B5" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="24">
         <v>1</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="25">
         <v>2458483.2110000001</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="26">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="25">
         <v>2458483.2118000002</v>
       </c>
-      <c r="G5" s="53">
+      <c r="G5" s="52">
         <f t="shared" ref="G5:G23" si="0">ABS((F5-D5)/E5)</f>
         <v>0.23529412882292974</v>
       </c>
-      <c r="H5" s="26">
+      <c r="H5" s="25">
         <v>2458483.2052000002</v>
       </c>
-      <c r="I5" s="53">
+      <c r="I5" s="52">
         <f t="shared" ref="I5:I23" si="1">ABS((H5-D5)/E5)</f>
         <v>1.705882331246839</v>
       </c>
-      <c r="J5" s="26">
+      <c r="J5" s="25">
         <v>2458482.8635</v>
       </c>
-      <c r="K5" s="53">
+      <c r="K5" s="52">
         <f t="shared" ref="K5:K23" si="2">ABS((J5-D5)/E5)</f>
         <v>102.20588239676813</v>
       </c>
       <c r="M5" s="8"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="23">
+      <c r="A6" s="22">
         <v>9</v>
       </c>
-      <c r="B6" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="25">
+      <c r="B6" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="24">
         <v>2</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="25">
         <v>2458565.0902</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="26">
         <v>3.2499999999999999E-3</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="25">
         <v>2458565.0959000001</v>
       </c>
-      <c r="G6" s="53">
+      <c r="G6" s="52">
         <f t="shared" si="0"/>
         <v>1.7538461834192276</v>
       </c>
-      <c r="H6" s="26">
+      <c r="H6" s="25">
         <v>2458565.0822999999</v>
       </c>
-      <c r="I6" s="53">
+      <c r="I6" s="52">
         <f t="shared" si="1"/>
         <v>2.4307692566743264</v>
       </c>
-      <c r="J6" s="26">
+      <c r="J6" s="25">
         <v>2458564.4419</v>
       </c>
-      <c r="K6" s="53">
+      <c r="K6" s="52">
         <f t="shared" si="2"/>
         <v>199.47692307715232</v>
       </c>
       <c r="M6" s="8"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="28">
+      <c r="A7" s="27">
         <v>12</v>
       </c>
-      <c r="B7" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="30">
+      <c r="B7" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="29">
         <v>3</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="30">
         <v>2458647.3328</v>
       </c>
-      <c r="E7" s="32">
+      <c r="E7" s="31">
         <v>4.4000000000000003E-3</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="30">
         <v>2458647.3298999998</v>
       </c>
-      <c r="G7" s="54">
+      <c r="G7" s="53">
         <f t="shared" si="0"/>
         <v>0.6590909536250612</v>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="30">
         <v>2458647.3202</v>
       </c>
-      <c r="I7" s="54">
+      <c r="I7" s="53">
         <f t="shared" si="1"/>
         <v>2.8636363673616536</v>
       </c>
-      <c r="J7" s="31">
+      <c r="J7" s="30">
         <v>2458646.4597</v>
       </c>
-      <c r="K7" s="54">
+      <c r="K7" s="53">
         <f t="shared" si="2"/>
         <v>198.43181817453691</v>
       </c>
       <c r="M7" s="8"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="23">
+      <c r="A8" s="22">
         <v>28</v>
       </c>
-      <c r="B8" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="25">
+      <c r="B8" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="24">
         <v>8</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="25">
         <v>2459065.2370000002</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="26">
         <v>2.3500000000000001E-3</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="25">
         <v>2459065.2407999998</v>
       </c>
-      <c r="G8" s="53">
+      <c r="G8" s="52">
         <f t="shared" si="0"/>
         <v>1.6170211057079598</v>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="25">
         <v>2459065.2357000001</v>
       </c>
-      <c r="I8" s="53">
+      <c r="I8" s="52">
         <f t="shared" si="1"/>
         <v>0.5531915404061053</v>
       </c>
-      <c r="J8" s="26">
+      <c r="J8" s="25">
         <v>2459064.2108999998</v>
       </c>
-      <c r="K8" s="53">
+      <c r="K8" s="52">
         <f t="shared" si="2"/>
         <v>436.63829802832703</v>
       </c>
       <c r="M8" s="8"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="23">
+      <c r="A9" s="22">
         <v>31</v>
       </c>
-      <c r="B9" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="25">
+      <c r="B9" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="24">
         <v>9</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="25">
         <v>2459148.4781999998</v>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="26">
         <v>2.65E-3</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="25">
         <v>2459148.4778999998</v>
       </c>
-      <c r="G9" s="53">
+      <c r="G9" s="52">
         <f t="shared" si="0"/>
         <v>0.11320753058172622</v>
       </c>
-      <c r="H9" s="26">
+      <c r="H9" s="25">
         <v>2459148.4284999999</v>
       </c>
-      <c r="I9" s="53">
+      <c r="I9" s="52">
         <f t="shared" si="1"/>
         <v>18.754716927431666</v>
       </c>
-      <c r="J9" s="26">
+      <c r="J9" s="25">
         <v>2459147.1962000001</v>
       </c>
-      <c r="K9" s="53">
+      <c r="K9" s="52">
         <f t="shared" si="2"/>
         <v>483.77358477632953</v>
       </c>
       <c r="M9" s="8"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="23">
+      <c r="A10" s="22">
         <v>34</v>
       </c>
-      <c r="B10" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="25">
-        <v>10</v>
-      </c>
-      <c r="D10" s="26">
+      <c r="B10" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="24">
+        <v>10</v>
+      </c>
+      <c r="D10" s="25">
         <v>2459231.1144000003</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="26">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="25">
         <v>2459231.1167000001</v>
       </c>
-      <c r="G10" s="53">
+      <c r="G10" s="52">
         <f t="shared" si="0"/>
         <v>1.0952380086694447</v>
       </c>
-      <c r="H10" s="26">
+      <c r="H10" s="25">
         <v>2459231.0216999999</v>
       </c>
-      <c r="I10" s="53">
+      <c r="I10" s="52">
         <f t="shared" si="1"/>
         <v>44.142857326992925</v>
       </c>
-      <c r="J10" s="26">
+      <c r="J10" s="25">
         <v>2459229.4999000002</v>
       </c>
-      <c r="K10" s="53">
+      <c r="K10" s="52">
         <f t="shared" si="2"/>
         <v>768.80952387693389</v>
       </c>
       <c r="M10" s="8"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="28">
+      <c r="A11" s="27">
         <v>37</v>
       </c>
-      <c r="B11" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="30">
+      <c r="B11" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="29">
         <v>11</v>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="30">
         <v>2459313.2535000001</v>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="31">
         <v>1.9E-3</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="30">
         <v>2459313.2577999998</v>
       </c>
-      <c r="G11" s="54">
+      <c r="G11" s="53">
         <f t="shared" si="0"/>
         <v>2.2631577265105749</v>
       </c>
-      <c r="H11" s="31">
+      <c r="H11" s="30">
         <v>2459313.1257000002</v>
       </c>
-      <c r="I11" s="54">
+      <c r="I11" s="53">
         <f t="shared" si="1"/>
         <v>67.263157842190637</v>
       </c>
-      <c r="J11" s="31">
+      <c r="J11" s="30">
         <v>2459311.2730999999</v>
       </c>
-      <c r="K11" s="54">
+      <c r="K11" s="53">
         <f t="shared" si="2"/>
         <v>1042.3157895964227</v>
       </c>
       <c r="M11" s="8"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="23">
+      <c r="A12" s="22">
         <v>61</v>
       </c>
-      <c r="B12" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="25">
+      <c r="B12" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="24">
         <v>19</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="25">
         <v>2459976.0493000001</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="26">
         <v>4.4000000000000003E-3</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="25">
         <v>2459976.0480999998</v>
       </c>
-      <c r="G12" s="53">
+      <c r="G12" s="52">
         <f t="shared" si="0"/>
         <v>0.27272733859717846</v>
       </c>
-      <c r="H12" s="26">
+      <c r="H12" s="25">
         <v>2459976.0643000002</v>
       </c>
-      <c r="I12" s="53">
+      <c r="I12" s="52">
         <f t="shared" si="1"/>
         <v>3.4090909387238999</v>
       </c>
-      <c r="J12" s="26">
+      <c r="J12" s="25">
         <v>2459973.1538</v>
       </c>
-      <c r="K12" s="53">
+      <c r="K12" s="52">
         <f t="shared" si="2"/>
         <v>658.06818184104156</v>
       </c>
       <c r="M12" s="8"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="23">
+      <c r="A13" s="22">
         <v>64</v>
       </c>
-      <c r="B13" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="33">
+      <c r="B13" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="32">
         <v>20</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="25">
         <v>2460059.6189000001</v>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="26">
         <v>2.3E-3</v>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="25">
         <v>2460059.6168</v>
       </c>
-      <c r="G13" s="53">
+      <c r="G13" s="52">
         <f t="shared" si="0"/>
         <v>0.91304354693578638</v>
       </c>
-      <c r="H13" s="26">
+      <c r="H13" s="25">
         <v>2460059.5575000001</v>
       </c>
-      <c r="I13" s="53">
+      <c r="I13" s="52">
         <f t="shared" si="1"/>
         <v>26.695652176504549</v>
       </c>
-      <c r="J13" s="26">
+      <c r="J13" s="25">
         <v>2460056.5010000002</v>
       </c>
-      <c r="K13" s="53">
+      <c r="K13" s="52">
         <f t="shared" si="2"/>
         <v>1355.6086956320898</v>
       </c>
       <c r="M13" s="8"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="28">
+      <c r="A14" s="27">
         <v>67</v>
       </c>
-      <c r="B14" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="34">
+      <c r="B14" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="33">
         <v>21</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="30">
         <v>2460142.6048000003</v>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="31">
         <v>2.2499999999999998E-3</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="30">
         <v>2460142.6061</v>
       </c>
-      <c r="G14" s="54">
+      <c r="G14" s="53">
         <f t="shared" si="0"/>
         <v>0.57777762413024902</v>
       </c>
-      <c r="H14" s="31">
+      <c r="H14" s="30">
         <v>2460142.4610000001</v>
       </c>
-      <c r="I14" s="54">
+      <c r="I14" s="53">
         <f t="shared" si="1"/>
         <v>63.911111197537849</v>
       </c>
-      <c r="J14" s="31">
+      <c r="J14" s="30">
         <v>2460139.1642999998</v>
       </c>
-      <c r="K14" s="54">
+      <c r="K14" s="53">
         <f t="shared" si="2"/>
         <v>1529.1111113296615</v>
       </c>
       <c r="M14" s="8"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="23">
+      <c r="A15" s="22">
         <v>89</v>
       </c>
-      <c r="B15" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="33">
+      <c r="B15" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="32">
         <v>28</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="25">
         <v>2460718.6126000001</v>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="26">
         <v>4.5799999999999999E-3</v>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="25">
         <v>2460718.6072</v>
       </c>
-      <c r="G15" s="53">
+      <c r="G15" s="52">
         <f t="shared" si="0"/>
         <v>1.1790393318932129</v>
       </c>
-      <c r="H15" s="26">
+      <c r="H15" s="25">
         <v>2460718.6047</v>
       </c>
-      <c r="I15" s="53">
+      <c r="I15" s="52">
         <f t="shared" si="1"/>
         <v>1.72489084807676</v>
       </c>
-      <c r="J15" s="26">
+      <c r="J15" s="25">
         <v>2460713.7359000002</v>
       </c>
-      <c r="K15" s="53">
+      <c r="K15" s="52">
         <f t="shared" si="2"/>
         <v>1064.7816593681491</v>
       </c>
       <c r="M15" s="8"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="23">
+      <c r="A16" s="22">
         <v>95</v>
       </c>
-      <c r="B16" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="33">
+      <c r="B16" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="32">
         <v>30</v>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="25">
         <v>2460886.2719999999</v>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="26">
         <v>4.5799999999999999E-3</v>
       </c>
-      <c r="F16" s="26">
+      <c r="F16" s="25">
         <v>2460886.2751000002</v>
       </c>
-      <c r="G16" s="53">
+      <c r="G16" s="52">
         <f t="shared" si="0"/>
         <v>0.67685596547272531</v>
       </c>
-      <c r="H16" s="26">
+      <c r="H16" s="25">
         <v>2460886.3358999998</v>
       </c>
-      <c r="I16" s="53">
+      <c r="I16" s="52">
         <f t="shared" si="1"/>
         <v>13.951965054602862</v>
       </c>
-      <c r="J16" s="26">
+      <c r="J16" s="25">
         <v>2460881.5249999999</v>
       </c>
-      <c r="K16" s="53">
+      <c r="K16" s="52">
         <f t="shared" si="2"/>
         <v>1036.4628820903763</v>
       </c>
       <c r="M16" s="8"/>
     </row>
     <row r="17" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="35">
+      <c r="A17" s="34">
         <v>97</v>
       </c>
-      <c r="B17" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="37">
+      <c r="B17" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="36">
         <v>31</v>
       </c>
-      <c r="D17" s="38">
+      <c r="D17" s="37">
         <v>2460970.0865000002</v>
       </c>
-      <c r="E17" s="39">
+      <c r="E17" s="38">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="F17" s="38">
+      <c r="F17" s="37">
         <v>2460970.0811999999</v>
       </c>
-      <c r="G17" s="55">
+      <c r="G17" s="54">
         <f t="shared" si="0"/>
         <v>0.88333338499069214</v>
       </c>
-      <c r="H17" s="38">
+      <c r="H17" s="37">
         <v>2460970.0865000002</v>
       </c>
-      <c r="I17" s="55">
+      <c r="I17" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J17" s="38">
+      <c r="J17" s="37">
         <v>2460965.2303999998</v>
       </c>
-      <c r="K17" s="55">
+      <c r="K17" s="54">
         <f t="shared" si="2"/>
         <v>809.35000007351243</v>
       </c>
       <c r="M17" s="8"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="23">
+      <c r="A18" s="22">
         <v>88</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="33">
+      <c r="C18" s="32">
         <v>0</v>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="25">
         <v>2460695.5345999999</v>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="26">
         <v>4.5799999999999999E-3</v>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="25">
         <v>2460695.5397999999</v>
       </c>
-      <c r="G18" s="53">
+      <c r="G18" s="52">
         <f t="shared" si="0"/>
         <v>1.1353711821301535</v>
       </c>
-      <c r="H18" s="26">
+      <c r="H18" s="25">
         <v>2460695.3920999998</v>
       </c>
-      <c r="I18" s="53">
+      <c r="I18" s="52">
         <f t="shared" si="1"/>
         <v>31.113537134171573</v>
       </c>
-      <c r="J18" s="26">
+      <c r="J18" s="25">
         <v>2460691.4147000001</v>
       </c>
-      <c r="K18" s="53">
+      <c r="K18" s="52">
         <f t="shared" si="2"/>
         <v>899.54148467597611</v>
       </c>
       <c r="M18" s="8"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="23">
+      <c r="A19" s="22">
         <v>89</v>
       </c>
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="33">
+      <c r="C19" s="32">
         <v>1</v>
       </c>
-      <c r="D19" s="26">
+      <c r="D19" s="25">
         <v>2460736.6348999999</v>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="26">
         <v>4.5799999999999999E-3</v>
       </c>
-      <c r="F19" s="26">
+      <c r="F19" s="25">
         <v>2460736.6342000002</v>
       </c>
-      <c r="G19" s="53">
+      <c r="G19" s="52">
         <f t="shared" si="0"/>
         <v>0.1528383716615527</v>
       </c>
-      <c r="H19" s="26">
+      <c r="H19" s="25">
         <v>2460736.4485999998</v>
       </c>
-      <c r="I19" s="53">
+      <c r="I19" s="52">
         <f t="shared" si="1"/>
         <v>40.676855933588143</v>
       </c>
-      <c r="J19" s="26">
+      <c r="J19" s="25">
         <v>2460732.3349000001</v>
       </c>
-      <c r="K19" s="53">
+      <c r="K19" s="52">
         <f t="shared" si="2"/>
         <v>938.86462878029158</v>
       </c>
       <c r="M19" s="8"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="23">
+      <c r="A20" s="22">
         <v>94</v>
       </c>
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="33">
+      <c r="C20" s="32">
         <v>4</v>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="25">
         <v>2460859.2275</v>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="26">
         <v>4.5799999999999999E-3</v>
       </c>
-      <c r="F20" s="26">
+      <c r="F20" s="25">
         <v>2460859.2245</v>
       </c>
-      <c r="G20" s="53">
+      <c r="G20" s="52">
         <f t="shared" si="0"/>
         <v>0.65502183975481054</v>
       </c>
-      <c r="H20" s="26">
+      <c r="H20" s="25">
         <v>2460858.9695000001</v>
       </c>
-      <c r="I20" s="53">
+      <c r="I20" s="52">
         <f t="shared" si="1"/>
         <v>56.331877710549854</v>
       </c>
-      <c r="J20" s="26">
+      <c r="J20" s="25">
         <v>2460854.4205</v>
       </c>
-      <c r="K20" s="53">
+      <c r="K20" s="52">
         <f t="shared" si="2"/>
         <v>1049.5633187837996</v>
       </c>
       <c r="M20" s="8"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="23">
+      <c r="A21" s="22">
         <v>95</v>
       </c>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="33">
+      <c r="C21" s="32">
         <v>5</v>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="25">
         <v>2460900.06</v>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="26">
         <v>4.5799999999999999E-3</v>
       </c>
-      <c r="F21" s="26">
+      <c r="F21" s="25">
         <v>2460900.0610000002</v>
       </c>
-      <c r="G21" s="53">
+      <c r="G21" s="52">
         <f t="shared" si="0"/>
         <v>0.21834064714252688</v>
       </c>
-      <c r="H21" s="26">
+      <c r="H21" s="25">
         <v>2460899.8029999998</v>
       </c>
-      <c r="I21" s="53">
+      <c r="I21" s="52">
         <f t="shared" si="1"/>
         <v>56.113537165080096</v>
       </c>
-      <c r="J21" s="26">
+      <c r="J21" s="25">
         <v>2460895.1200999999</v>
       </c>
-      <c r="K21" s="53">
+      <c r="K21" s="52">
         <f t="shared" si="2"/>
         <v>1078.5807860510904</v>
       </c>
       <c r="M21" s="8"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="23">
+      <c r="A22" s="22">
         <v>97</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="33">
+      <c r="C22" s="32">
         <v>6</v>
       </c>
-      <c r="D22" s="26">
+      <c r="D22" s="25">
         <v>2460940.8199999998</v>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="26">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="F22" s="26">
+      <c r="F22" s="25">
         <v>2460940.8517</v>
       </c>
-      <c r="G22" s="53">
+      <c r="G22" s="52">
         <f t="shared" si="0"/>
         <v>0.96060606566342432</v>
       </c>
-      <c r="H22" s="26">
+      <c r="H22" s="25">
         <v>2460940.6022999999</v>
       </c>
-      <c r="I22" s="53">
+      <c r="I22" s="52">
         <f t="shared" si="1"/>
         <v>6.5969696945764795</v>
       </c>
-      <c r="J22" s="26">
+      <c r="J22" s="25">
         <v>2460935.7941999999</v>
       </c>
-      <c r="K22" s="53">
+      <c r="K22" s="52">
         <f t="shared" si="2"/>
         <v>152.29696969529894</v>
       </c>
       <c r="M22" s="8"/>
     </row>
     <row r="23" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="35">
+      <c r="A23" s="34">
         <v>97</v>
       </c>
-      <c r="B23" s="36" t="s">
+      <c r="B23" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="37">
+      <c r="C23" s="36">
         <v>7</v>
       </c>
-      <c r="D23" s="38">
+      <c r="D23" s="37">
         <f>2460981.71</f>
         <v>2460981.71</v>
       </c>
-      <c r="E23" s="39">
+      <c r="E23" s="38">
         <v>0.01</v>
       </c>
-      <c r="F23" s="38">
+      <c r="F23" s="37">
         <v>2460981.7239999999</v>
       </c>
-      <c r="G23" s="55">
+      <c r="G23" s="54">
         <f t="shared" si="0"/>
         <v>1.3999999966472387</v>
       </c>
-      <c r="H23" s="38">
+      <c r="H23" s="37">
         <v>2460981.4937</v>
       </c>
-      <c r="I23" s="55">
+      <c r="I23" s="54">
         <f t="shared" si="1"/>
         <v>21.629999997094274</v>
       </c>
-      <c r="J23" s="38">
+      <c r="J23" s="37">
         <v>2460976.5742000001</v>
       </c>
-      <c r="K23" s="55">
+      <c r="K23" s="54">
         <f t="shared" si="2"/>
         <v>513.57999998144805</v>
       </c>
@@ -2524,19 +2572,19 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="70" t="s">
+      <c r="A2" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="70" t="s">
+      <c r="B2" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="70" t="s">
+      <c r="C2" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="71">
+      <c r="D2" s="70">
         <v>0.88500000000000001</v>
       </c>
-      <c r="E2" s="71">
+      <c r="E2" s="70">
         <v>0.88500000000000001</v>
       </c>
     </row>
@@ -2550,10 +2598,10 @@
       <c r="C3" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="64">
+      <c r="D3" s="63">
         <v>2.1278000000000001</v>
       </c>
-      <c r="E3" s="64">
+      <c r="E3" s="63">
         <v>2.1511999999999998</v>
       </c>
     </row>
@@ -2564,10 +2612,10 @@
       <c r="B4" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="64">
+      <c r="D4" s="63">
         <v>0.24979999999999999</v>
       </c>
-      <c r="E4" s="65">
+      <c r="E4" s="64">
         <v>0.25019847194350425</v>
       </c>
     </row>
@@ -2581,10 +2629,10 @@
       <c r="C5" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="66">
+      <c r="D5" s="65">
         <v>91.1</v>
       </c>
-      <c r="E5" s="66">
+      <c r="E5" s="65">
         <v>88.763733999999999</v>
       </c>
     </row>
@@ -2598,10 +2646,10 @@
       <c r="C6" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="64">
+      <c r="D6" s="63">
         <v>41.787799999999997</v>
       </c>
-      <c r="E6" s="65">
+      <c r="E6" s="64">
         <v>41.781945999999998</v>
       </c>
     </row>
@@ -2615,10 +2663,10 @@
       <c r="C7" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="64">
+      <c r="D7" s="63">
         <v>0.24</v>
       </c>
-      <c r="E7" s="64">
+      <c r="E7" s="63">
         <v>0</v>
       </c>
     </row>
@@ -2632,10 +2680,10 @@
       <c r="C8" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="66">
+      <c r="D8" s="65">
         <v>275.8</v>
       </c>
-      <c r="E8" s="66">
+      <c r="E8" s="65">
         <v>276.76663869301791</v>
       </c>
     </row>
@@ -2649,10 +2697,10 @@
       <c r="C9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="67">
+      <c r="D9" s="66">
         <v>339.54</v>
       </c>
-      <c r="E9" s="67">
+      <c r="E9" s="66">
         <v>337.15902078899757</v>
       </c>
     </row>
@@ -2666,10 +2714,10 @@
       <c r="C10" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="64">
+      <c r="D10" s="63">
         <v>2.6315</v>
       </c>
-      <c r="E10" s="65">
+      <c r="E10" s="64">
         <v>2.63849</v>
       </c>
     </row>
@@ -2680,10 +2728,10 @@
       <c r="B11" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="64">
+      <c r="D11" s="63">
         <v>3.7699999999999997E-2</v>
       </c>
-      <c r="E11" s="65">
+      <c r="E11" s="64">
         <v>3.5024375561053193E-2</v>
       </c>
     </row>
@@ -2697,10 +2745,10 @@
       <c r="C12" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="64">
+      <c r="D12" s="63">
         <v>89.69</v>
       </c>
-      <c r="E12" s="66">
+      <c r="E12" s="65">
         <v>89.711567000000002</v>
       </c>
     </row>
@@ -2717,7 +2765,7 @@
       <c r="D13" s="6">
         <v>81.463099999999997</v>
       </c>
-      <c r="E13" s="64">
+      <c r="E13" s="63">
         <v>81.820097000000004</v>
       </c>
     </row>
@@ -2731,10 +2779,10 @@
       <c r="C14" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="64">
+      <c r="D14" s="63">
         <v>0.8</v>
       </c>
-      <c r="E14" s="64">
+      <c r="E14" s="63">
         <v>-2.016956</v>
       </c>
     </row>
@@ -2748,10 +2796,10 @@
       <c r="C15" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="68">
+      <c r="D15" s="67">
         <v>298.89</v>
       </c>
-      <c r="E15" s="66">
+      <c r="E15" s="65">
         <v>303.62478284868769</v>
       </c>
     </row>
@@ -2765,10 +2813,10 @@
       <c r="C16" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="69">
+      <c r="D16" s="68">
         <v>142.72</v>
       </c>
-      <c r="E16" s="67">
+      <c r="E16" s="66">
         <v>137.89365221593033</v>
       </c>
     </row>

--- a/results/TOI-4504 Comparison.xlsx
+++ b/results/TOI-4504 Comparison.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meine Ablage\Python\curvesim\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4E68342-238C-4AAC-80F8-0E6405423D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3764609C-A40B-446B-AA5E-80FBF34319C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="1000" xr2:uid="{6919DDE8-15F9-45FB-B5F7-4209377AF865}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="52">
   <si>
     <t>d</t>
   </si>
@@ -179,10 +179,6 @@
     <t>sim2</t>
   </si>
   <si>
-    <t>Michaela
-Trifon</t>
-  </si>
-  <si>
     <t>Uli
 jacobimasses =true</t>
   </si>
@@ -192,6 +188,18 @@
   </si>
   <si>
     <t>chi_squared_tt</t>
+  </si>
+  <si>
+    <t>Michaela
+Trifon
+20.03.2026</t>
+  </si>
+  <si>
+    <t>Almenara
+Table 1</t>
+  </si>
+  <si>
+    <t>BJD TDB</t>
   </si>
 </sst>
 </file>
@@ -479,7 +487,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -640,6 +648,10 @@
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -979,7 +991,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CBA9F35-6018-400E-B5CC-CA22C216F82B}">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
@@ -987,9 +999,10 @@
     <col min="4" max="5" width="13.85546875" customWidth="1"/>
     <col min="6" max="6" width="13.85546875" style="76" customWidth="1"/>
     <col min="7" max="7" width="13.85546875" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>13</v>
       </c>
@@ -1000,24 +1013,31 @@
         <v>15</v>
       </c>
       <c r="D1" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="74" t="s">
         <v>47</v>
-      </c>
-      <c r="F1" s="74" t="s">
-        <v>48</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H1" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
+      <c r="B2" s="84" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>0</v>
+      </c>
       <c r="D2" s="15">
         <v>2458400</v>
       </c>
@@ -1030,8 +1050,11 @@
       <c r="G2" s="18">
         <v>2458400</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="85">
+        <v>2460886.2837999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1054,7 +1077,7 @@
         <v>0.877</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -1076,8 +1099,9 @@
       <c r="G4" s="4">
         <v>0.93100000000000005</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1100,8 +1124,12 @@
         <f>G$3*G18*G$33</f>
         <v>2.0212340212017694</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5" s="12">
+        <f>H$3*H18*H$33</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1121,7 +1149,7 @@
         <v>1.012</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1142,8 +1170,12 @@
         <f>G14*G14+G15*G15</f>
         <v>0.269924</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H7" s="12">
+        <f>H14*H14+H15*H15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1163,7 +1195,7 @@
         <v>91.1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1186,7 +1218,7 @@
         <v>41.8</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -1206,7 +1238,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -1230,8 +1262,12 @@
         <f>MOD(DEGREES(ATAN2(G15,G14)),360)</f>
         <v>265.58437826536226</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H11" s="19" t="e">
+        <f>MOD(DEGREES(ATAN2(H15,H14)),360)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>7</v>
       </c>
@@ -1257,8 +1293,12 @@
         <f>MOD(DEGREES(((G$2-G13)/G9)*2*PI()),360)</f>
         <v>173.11004784528578</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H12" s="73" t="e">
+        <f>MOD(DEGREES(((H$2-H13)/H9)*2*PI()),360)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -1275,7 +1315,7 @@
         <v>2458421.7000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -1286,7 +1326,7 @@
         <v>-0.51800000000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -1297,7 +1337,7 @@
         <v>-0.04</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -1308,7 +1348,7 @@
         <v>-0.24845565999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -1319,7 +1359,7 @@
         <v>2.9479829999999999E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>7</v>
       </c>
@@ -1342,8 +1382,9 @@
       <c r="G18" s="14">
         <v>2.2000000000000001E-3</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H18" s="14"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>10</v>
       </c>
@@ -1366,8 +1407,12 @@
         <f>G$3*G32*G$33</f>
         <v>2.5908545180859042</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H19" s="12">
+        <f>H$3*H32*H$33</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1387,7 +1432,7 @@
         <v>0.98970000000000002</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -1408,8 +1453,12 @@
         <f>G28*G28+G29*G29</f>
         <v>3.8800000000000001E-2</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H21" s="12">
+        <f>H28*H28+H29*H29</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -1429,7 +1478,7 @@
         <v>89.69</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -1452,7 +1501,7 @@
         <v>81.81</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>10</v>
       </c>
@@ -1472,7 +1521,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>10</v>
       </c>
@@ -1496,8 +1545,12 @@
         <f>MOD(DEGREES(ATAN2(G29,G28)),360)</f>
         <v>293.96248897457815</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H25" s="13" t="e">
+        <f>MOD(DEGREES(ATAN2(H29,H28)),360)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>10</v>
       </c>
@@ -1521,8 +1574,12 @@
         <f>MOD(DEGREES(((G$2-G27)/G23)*2*PI()),360)</f>
         <v>353.84598459790249</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H26" s="72" t="e">
+        <f>MOD(DEGREES(((H$2-H27)/H23)*2*PI()),360)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>10</v>
       </c>
@@ -1538,8 +1595,9 @@
       <c r="G27" s="8">
         <v>2458401.3985000001</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H27" s="8"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>10</v>
       </c>
@@ -1550,7 +1608,7 @@
         <v>-0.18</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>10</v>
       </c>
@@ -1561,7 +1619,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>10</v>
       </c>
@@ -1572,7 +1630,7 @@
         <v>-2.9164160000000001E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>10</v>
       </c>
@@ -1583,7 +1641,7 @@
         <v>1.9394809999999998E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>10</v>
       </c>
@@ -1606,8 +1664,9 @@
       <c r="G32" s="4">
         <v>2.82E-3</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H32" s="17"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>30</v>
       </c>
@@ -1626,10 +1685,13 @@
       <c r="G33">
         <v>1047.5971914594015</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" s="63" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H33">
+        <v>1047.5971914594015</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" s="63" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E34" s="63">
         <v>25.03</v>

--- a/results/TOI-4504 Comparison.xlsx
+++ b/results/TOI-4504 Comparison.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meine Ablage\Python\curvesim\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3764609C-A40B-446B-AA5E-80FBF34319C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D213910-7B4A-420F-8CEC-F1B5166F177C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="1000" xr2:uid="{6919DDE8-15F9-45FB-B5F7-4209377AF865}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="55">
   <si>
     <t>d</t>
   </si>
@@ -195,11 +195,21 @@
 20.03.2026</t>
   </si>
   <si>
+    <t>BJD TDB</t>
+  </si>
+  <si>
+    <t>Limbdarkening q1</t>
+  </si>
+  <si>
+    <t>Limbdarkening q2</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
     <t>Almenara
-Table 1</t>
-  </si>
-  <si>
-    <t>BJD TDB</t>
+Table 1
+Median</t>
   </si>
 </sst>
 </file>
@@ -212,7 +222,7 @@
     <numFmt numFmtId="166" formatCode="0.0000"/>
     <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -284,6 +294,21 @@
     <font>
       <sz val="11"/>
       <color theme="0" tint="-0.499984740745262"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -487,7 +512,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -519,9 +544,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -631,9 +653,6 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -643,15 +662,28 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -991,13 +1023,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CBA9F35-6018-400E-B5CC-CA22C216F82B}">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="13.85546875" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" style="76" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="70" customWidth="1"/>
     <col min="7" max="7" width="13.85546875" customWidth="1"/>
     <col min="8" max="8" width="14.7109375" customWidth="1"/>
   </cols>
@@ -1018,22 +1050,22 @@
       <c r="E1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="F1" s="74" t="s">
+      <c r="F1" s="68" t="s">
         <v>47</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="84" t="s">
-        <v>51</v>
+      <c r="B2" s="66" t="s">
+        <v>50</v>
       </c>
       <c r="C2" s="16" t="s">
         <v>0</v>
@@ -1044,13 +1076,13 @@
       <c r="E2" s="15">
         <v>2458400</v>
       </c>
-      <c r="F2" s="75">
+      <c r="F2" s="69">
         <v>2458400</v>
       </c>
       <c r="G2" s="18">
         <v>2458400</v>
       </c>
-      <c r="H2" s="85">
+      <c r="H2" s="91">
         <v>2460886.2837999999</v>
       </c>
     </row>
@@ -1070,83 +1102,72 @@
       <c r="E3">
         <v>0.88500000000000001</v>
       </c>
-      <c r="F3" s="76">
+      <c r="F3" s="70">
         <v>0.88500000000000001</v>
       </c>
       <c r="G3">
         <v>0.877</v>
       </c>
+      <c r="H3">
+        <v>0.877</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="77">
         <v>0.92</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="77">
         <v>0.92</v>
       </c>
-      <c r="F4" s="77">
+      <c r="F4" s="78">
         <v>0.92</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="77">
         <v>0.93100000000000005</v>
       </c>
-      <c r="H4" s="4"/>
+      <c r="H4" s="77">
+        <v>0.93100000000000005</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5">
-        <v>2.1511999999999998</v>
-      </c>
-      <c r="E5">
-        <v>2.1278000000000001</v>
-      </c>
-      <c r="F5" s="76">
-        <v>2.1278000000000001</v>
-      </c>
-      <c r="G5" s="12">
-        <f>G$3*G18*G$33</f>
-        <v>2.0212340212017694</v>
-      </c>
-      <c r="H5" s="12">
-        <f>H$3*H18*H$33</f>
-        <v>0</v>
+      <c r="A5" s="77" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="79" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77">
+        <v>0.3</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6">
-        <v>1.0249999999999999</v>
-      </c>
-      <c r="E6">
-        <v>1.012</v>
-      </c>
-      <c r="F6" s="76">
-        <v>1.012</v>
+      <c r="A6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4">
+        <v>0.32</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -1154,25 +1175,27 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="12">
-        <f>SQRT(D16*D16+D17*D17)</f>
-        <v>0.25019847194350425</v>
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>2.1511999999999998</v>
       </c>
       <c r="E7">
-        <v>0.24979999999999999</v>
-      </c>
-      <c r="F7" s="76">
-        <v>0.24979999999999999</v>
+        <v>2.1278000000000001</v>
+      </c>
+      <c r="F7" s="70">
+        <v>2.1278000000000001</v>
       </c>
       <c r="G7" s="12">
-        <f>G14*G14+G15*G15</f>
-        <v>0.269924</v>
+        <f>G$3*G21*G$37</f>
+        <v>2.0212340212017694</v>
       </c>
       <c r="H7" s="12">
-        <f>H14*H14+H15*H15</f>
-        <v>0</v>
+        <f>H$3*H21*H$37</f>
+        <v>2.0257358606126279</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -1180,19 +1203,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="3">
-        <v>88.763733999999999</v>
-      </c>
-      <c r="E8" s="3">
-        <v>91.1</v>
-      </c>
-      <c r="F8" s="78">
-        <v>91.1</v>
+        <v>21</v>
+      </c>
+      <c r="D8">
+        <v>1.0249999999999999</v>
+      </c>
+      <c r="E8">
+        <v>1.012</v>
+      </c>
+      <c r="F8" s="70">
+        <v>1.012</v>
+      </c>
+      <c r="H8" s="79">
+        <v>0.999</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -1200,22 +1226,24 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="8">
-        <v>41.781945999999998</v>
+        <v>5</v>
+      </c>
+      <c r="D9" s="12">
+        <f>SQRT(D19*D19+D20*D20)</f>
+        <v>0.25019847194350425</v>
       </c>
       <c r="E9">
-        <v>41.787799999999997</v>
-      </c>
-      <c r="F9" s="76">
-        <v>41.787799999999997</v>
-      </c>
-      <c r="G9">
-        <v>41.8</v>
+        <v>0.24979999999999999</v>
+      </c>
+      <c r="F9" s="70">
+        <v>0.24979999999999999</v>
+      </c>
+      <c r="G9" s="12">
+        <f>G17*G17+G18*G18</f>
+        <v>0.269924</v>
+      </c>
+      <c r="H9" s="61">
+        <v>0.29299999999999998</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -1223,19 +1251,22 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C10" t="s">
         <v>22</v>
       </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0.24</v>
-      </c>
-      <c r="F10" s="76">
-        <v>0.24</v>
+      <c r="D10" s="3">
+        <v>88.763733999999999</v>
+      </c>
+      <c r="E10" s="3">
+        <v>91.1</v>
+      </c>
+      <c r="F10" s="72">
+        <v>91.1</v>
+      </c>
+      <c r="H10" s="3">
+        <v>88.980999999999995</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -1243,59 +1274,48 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="8">
+        <v>41.781945999999998</v>
+      </c>
+      <c r="E11">
+        <v>41.787799999999997</v>
+      </c>
+      <c r="F11" s="70">
+        <v>41.787799999999997</v>
+      </c>
+      <c r="G11">
+        <v>41.8</v>
+      </c>
+      <c r="H11">
+        <v>40.820399999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="19">
-        <f>MOD(DEGREES(ATAN2(D17,D16)),360)</f>
-        <v>276.76663869301791</v>
-      </c>
-      <c r="E11" s="3">
-        <v>275.8</v>
-      </c>
-      <c r="F11" s="78">
-        <v>275.8</v>
-      </c>
-      <c r="G11" s="19">
-        <f>MOD(DEGREES(ATAN2(G15,G14)),360)</f>
-        <v>265.58437826536226</v>
-      </c>
-      <c r="H11" s="19" t="e">
-        <f>MOD(DEGREES(ATAN2(H15,H14)),360)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="20">
-        <f>MOD(DEGREES(((D$2-D13)/D9)*2*PI()),360)</f>
-        <v>337.15902078899757</v>
-      </c>
-      <c r="E12" s="21">
-        <f>-20.46+360</f>
-        <v>339.54</v>
-      </c>
-      <c r="F12" s="79">
-        <f>-20.46+360</f>
-        <v>339.54</v>
-      </c>
-      <c r="G12" s="73">
-        <f>MOD(DEGREES(((G$2-G13)/G9)*2*PI()),360)</f>
-        <v>173.11004784528578</v>
-      </c>
-      <c r="H12" s="73" t="e">
-        <f>MOD(DEGREES(((H$2-H13)/H9)*2*PI()),360)</f>
-        <v>#DIV/0!</v>
+      <c r="D12" s="80">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0.24</v>
+      </c>
+      <c r="F12" s="70">
+        <v>0.24</v>
+      </c>
+      <c r="H12" s="89">
+        <v>182.03</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -1303,38 +1323,74 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="2">
-        <v>2458360.8689999999</v>
-      </c>
-      <c r="G13">
-        <v>2458421.7000000002</v>
+        <v>22</v>
+      </c>
+      <c r="D13" s="13">
+        <f>MOD(DEGREES(ATAN2(D20,D19)),360)</f>
+        <v>276.76663869301791</v>
+      </c>
+      <c r="E13" s="1">
+        <v>275.8</v>
+      </c>
+      <c r="F13" s="74">
+        <v>275.8</v>
+      </c>
+      <c r="G13" s="13">
+        <f>MOD(DEGREES(ATAN2(G18,G17)),360)</f>
+        <v>265.58437826536226</v>
+      </c>
+      <c r="H13" s="1">
+        <v>195.97</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="A14" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B14" t="s">
-        <v>24</v>
-      </c>
-      <c r="G14">
-        <v>-0.51800000000000002</v>
+      <c r="B14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="81">
+        <f>MOD(DEGREES(((D$2-D16)/D11)*2*PI()),360)</f>
+        <v>337.15902078899757</v>
+      </c>
+      <c r="E14" s="9">
+        <f>-20.46+360</f>
+        <v>339.54</v>
+      </c>
+      <c r="F14" s="75">
+        <f>-20.46+360</f>
+        <v>339.54</v>
+      </c>
+      <c r="G14" s="92">
+        <f>MOD(DEGREES(((G$2-G16)/G11)*2*PI()),360)</f>
+        <v>173.11004784528578</v>
+      </c>
+      <c r="H14" s="65">
+        <f>166.28</f>
+        <v>166.28</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="A15" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="B15" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15">
-        <v>-0.04</v>
+      <c r="B15" s="79" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="77"/>
+      <c r="D15" s="82"/>
+      <c r="E15" s="83"/>
+      <c r="F15" s="84"/>
+      <c r="G15" s="85"/>
+      <c r="H15" s="86">
+        <v>0.22209999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1342,10 +1398,16 @@
         <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16">
-        <v>-0.24845565999999999</v>
+        <v>29</v>
+      </c>
+      <c r="C16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>2458360.8689999999</v>
+      </c>
+      <c r="G16">
+        <v>2458421.7000000002</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1353,109 +1415,71 @@
         <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17">
-        <v>2.9479829999999999E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G17">
+        <v>-0.51800000000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="14">
-        <f>D5/D$3/D$33</f>
-        <v>2.3202949407401465E-3</v>
-      </c>
-      <c r="E18" s="14">
-        <f>E5/E$3/E$33</f>
-        <v>2.2950555852114564E-3</v>
-      </c>
-      <c r="F18" s="80">
-        <f>F5/F$3/F$33</f>
-        <v>2.2950555852114564E-3</v>
-      </c>
-      <c r="G18" s="14">
-        <v>2.2000000000000001E-3</v>
-      </c>
-      <c r="H18" s="14"/>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18">
+        <v>-0.04</v>
+      </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="8">
-        <v>2.63849</v>
-      </c>
-      <c r="E19">
-        <v>2.6315</v>
-      </c>
-      <c r="F19" s="76">
-        <v>2.6315</v>
-      </c>
-      <c r="G19" s="12">
-        <f>G$3*G32*G$33</f>
-        <v>2.5908545180859042</v>
-      </c>
-      <c r="H19" s="12">
-        <f>H$3*H32*H$33</f>
-        <v>0</v>
+        <v>27</v>
+      </c>
+      <c r="D19">
+        <v>-0.24845565999999999</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D20">
-        <v>0.9738</v>
-      </c>
-      <c r="E20">
-        <v>0.98970000000000002</v>
-      </c>
-      <c r="F20" s="76">
-        <v>0.98970000000000002</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" t="s">
-        <v>5</v>
-      </c>
-      <c r="D21" s="12">
-        <f>SQRT(D30*D30+D31*D31)</f>
-        <v>3.5024375561053193E-2</v>
-      </c>
-      <c r="E21" s="8">
-        <v>3.5924999999999999E-2</v>
-      </c>
-      <c r="F21" s="76">
-        <v>3.7699999999999997E-2</v>
-      </c>
-      <c r="G21" s="12">
-        <f>G28*G28+G29*G29</f>
-        <v>3.8800000000000001E-2</v>
-      </c>
-      <c r="H21" s="12">
-        <f>H28*H28+H29*H29</f>
-        <v>0</v>
+        <v>2.9479829999999999E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="5"/>
+      <c r="D21" s="14">
+        <f>D7/D$3/D$37</f>
+        <v>2.3202949407401465E-3</v>
+      </c>
+      <c r="E21" s="14">
+        <f>E7/E$3/E$37</f>
+        <v>2.2950555852114564E-3</v>
+      </c>
+      <c r="F21" s="73">
+        <f>F7/F$3/F$37</f>
+        <v>2.2950555852114564E-3</v>
+      </c>
+      <c r="G21" s="14">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="H21" s="14">
+        <f>220.49/100000</f>
+        <v>2.2049000000000001E-3</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1463,19 +1487,27 @@
         <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" s="3">
-        <v>89.711567000000002</v>
+        <v>20</v>
+      </c>
+      <c r="D22" s="8">
+        <v>2.63849</v>
       </c>
       <c r="E22">
-        <v>89.69</v>
-      </c>
-      <c r="F22" s="76">
-        <v>89.69</v>
+        <v>2.6315</v>
+      </c>
+      <c r="F22" s="70">
+        <v>2.6315</v>
+      </c>
+      <c r="G22" s="12">
+        <f>G$3*G36*G$37</f>
+        <v>2.5908545180859042</v>
+      </c>
+      <c r="H22" s="12">
+        <f>H$3*H36*H$37</f>
+        <v>2.5877307927804103</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1483,22 +1515,22 @@
         <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C23" t="s">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="D23">
-        <v>81.820097000000004</v>
-      </c>
-      <c r="E23" s="71">
-        <v>81.821389999999994</v>
-      </c>
-      <c r="F23" s="76">
-        <v>81.463099999999997</v>
-      </c>
-      <c r="G23">
-        <v>81.81</v>
+        <v>0.9738</v>
+      </c>
+      <c r="E23">
+        <v>0.98970000000000002</v>
+      </c>
+      <c r="F23" s="70">
+        <v>0.98970000000000002</v>
+      </c>
+      <c r="H23">
+        <v>0.998</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1506,19 +1538,24 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24">
-        <v>-2.016956</v>
-      </c>
-      <c r="E24">
-        <v>0.8</v>
-      </c>
-      <c r="F24" s="76">
-        <v>0.8</v>
+        <v>5</v>
+      </c>
+      <c r="D24" s="12">
+        <f>SQRT(D34*D34+D35*D35)</f>
+        <v>3.5024375561053193E-2</v>
+      </c>
+      <c r="E24" s="8">
+        <v>3.5924999999999999E-2</v>
+      </c>
+      <c r="F24" s="70">
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="G24" s="12">
+        <f>G32*G32+G33*G33</f>
+        <v>3.8800000000000001E-2</v>
+      </c>
+      <c r="H24" s="61">
+        <v>4.9889999999999997E-2</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1526,57 +1563,48 @@
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C25" t="s">
         <v>22</v>
       </c>
-      <c r="D25" s="19">
-        <f>MOD(DEGREES(ATAN2(D31,D30)),360)</f>
-        <v>303.62478284868769</v>
-      </c>
-      <c r="E25" s="1">
-        <v>300.97730300000001</v>
-      </c>
-      <c r="F25" s="81">
-        <v>298.89</v>
-      </c>
-      <c r="G25" s="13">
-        <f>MOD(DEGREES(ATAN2(G29,G28)),360)</f>
-        <v>293.96248897457815</v>
-      </c>
-      <c r="H25" s="13" t="e">
-        <f>MOD(DEGREES(ATAN2(H29,H28)),360)</f>
-        <v>#DIV/0!</v>
+      <c r="D25" s="3">
+        <v>89.711567000000002</v>
+      </c>
+      <c r="E25">
+        <v>89.69</v>
+      </c>
+      <c r="F25" s="70">
+        <v>89.69</v>
+      </c>
+      <c r="H25">
+        <v>89.543000000000006</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D26" s="20">
-        <f>MOD(DEGREES(((D$2-D27)/D23)*2*PI()),360)</f>
-        <v>137.89365221593033</v>
-      </c>
-      <c r="E26" s="9">
-        <v>140.63120000000001</v>
-      </c>
-      <c r="F26" s="82">
-        <v>142.72</v>
-      </c>
-      <c r="G26" s="72">
-        <f>MOD(DEGREES(((G$2-G27)/G23)*2*PI()),360)</f>
-        <v>353.84598459790249</v>
-      </c>
-      <c r="H26" s="72" t="e">
-        <f>MOD(DEGREES(((H$2-H27)/H23)*2*PI()),360)</f>
-        <v>#DIV/0!</v>
+      <c r="A26" t="s">
+        <v>10</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2">
+        <v>81.820097000000004</v>
+      </c>
+      <c r="E26" s="87">
+        <v>81.821389999999994</v>
+      </c>
+      <c r="F26" s="88">
+        <v>81.463099999999997</v>
+      </c>
+      <c r="G26">
+        <v>81.81</v>
+      </c>
+      <c r="H26" s="2">
+        <v>84.072500000000005</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1584,50 +1612,94 @@
         <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>0</v>
-      </c>
-      <c r="D27" s="8">
-        <v>2458368.6598</v>
-      </c>
-      <c r="G27" s="8">
-        <v>2458401.3985000001</v>
-      </c>
-      <c r="H27" s="8"/>
+        <v>22</v>
+      </c>
+      <c r="D27">
+        <v>-2.016956</v>
+      </c>
+      <c r="E27">
+        <v>0.8</v>
+      </c>
+      <c r="F27" s="70">
+        <v>0.8</v>
+      </c>
+      <c r="H27" s="90">
+        <v>180</v>
+      </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>24</v>
-      </c>
-      <c r="G28">
-        <v>-0.18</v>
+        <v>9</v>
+      </c>
+      <c r="C28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D28" s="13">
+        <f>MOD(DEGREES(ATAN2(D35,D34)),360)</f>
+        <v>303.62478284868769</v>
+      </c>
+      <c r="E28" s="1">
+        <v>300.97730300000001</v>
+      </c>
+      <c r="F28" s="74">
+        <v>298.89</v>
+      </c>
+      <c r="G28" s="13">
+        <f>MOD(DEGREES(ATAN2(G33,G32)),360)</f>
+        <v>293.96248897457815</v>
+      </c>
+      <c r="H28" s="1">
+        <v>178.51</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>10</v>
-      </c>
-      <c r="B29" t="s">
-        <v>23</v>
-      </c>
-      <c r="G29">
-        <v>0.08</v>
+      <c r="A29" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" s="81">
+        <f>MOD(DEGREES(((D$2-D31)/D26)*2*PI()),360)</f>
+        <v>137.89365221593033</v>
+      </c>
+      <c r="E29" s="9">
+        <v>140.63120000000001</v>
+      </c>
+      <c r="F29" s="75">
+        <v>142.72</v>
+      </c>
+      <c r="G29" s="92">
+        <f>MOD(DEGREES(((G$2-G31)/G26)*2*PI()),360)</f>
+        <v>353.84598459790249</v>
+      </c>
+      <c r="H29" s="65">
+        <v>277.3</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>10</v>
-      </c>
-      <c r="B30" t="s">
-        <v>27</v>
-      </c>
-      <c r="D30">
-        <v>-2.9164160000000001E-2</v>
+      <c r="A30" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="B30" s="79" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" s="77"/>
+      <c r="D30" s="82"/>
+      <c r="E30" s="83"/>
+      <c r="F30" s="84"/>
+      <c r="G30" s="85"/>
+      <c r="H30" s="86">
+        <v>0.35949999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1635,65 +1707,118 @@
         <v>10</v>
       </c>
       <c r="B31" t="s">
-        <v>28</v>
-      </c>
-      <c r="D31">
-        <v>1.9394809999999998E-2</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C31" t="s">
+        <v>0</v>
+      </c>
+      <c r="D31" s="8">
+        <v>2458368.6598</v>
+      </c>
+      <c r="G31" s="8">
+        <v>2458401.3985000001</v>
+      </c>
+      <c r="H31" s="8"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="17">
-        <f>D19/D$3/D$33</f>
-        <v>2.8458883405510739E-3</v>
-      </c>
-      <c r="E32" s="17">
-        <f>E19/E$3/E$33</f>
-        <v>2.8383488920405799E-3</v>
-      </c>
-      <c r="F32" s="83">
-        <f>F19/F$3/F$33</f>
-        <v>2.8383488920405799E-3</v>
-      </c>
-      <c r="G32" s="4">
-        <v>2.82E-3</v>
-      </c>
-      <c r="H32" s="17"/>
+      <c r="A32" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32" t="s">
+        <v>24</v>
+      </c>
+      <c r="G32">
+        <v>-0.18</v>
+      </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33" t="s">
+        <v>23</v>
+      </c>
+      <c r="G33">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" t="s">
+        <v>27</v>
+      </c>
+      <c r="D34">
+        <v>-2.9164160000000001E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>10</v>
+      </c>
+      <c r="B35" t="s">
+        <v>28</v>
+      </c>
+      <c r="D35">
+        <v>1.9394809999999998E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="4"/>
+      <c r="D36" s="17">
+        <f>D22/D$3/D$37</f>
+        <v>2.8458883405510739E-3</v>
+      </c>
+      <c r="E36" s="17">
+        <f>E22/E$3/E$37</f>
+        <v>2.8383488920405799E-3</v>
+      </c>
+      <c r="F36" s="76">
+        <f>F22/F$3/F$37</f>
+        <v>2.8383488920405799E-3</v>
+      </c>
+      <c r="G36" s="4">
+        <v>2.82E-3</v>
+      </c>
+      <c r="H36" s="17">
+        <v>2.8165999999999998E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>30</v>
       </c>
-      <c r="C33">
+      <c r="C37">
         <v>1047.5971914594015</v>
       </c>
-      <c r="D33">
+      <c r="D37">
         <v>1047.5971914594015</v>
       </c>
-      <c r="E33">
+      <c r="E37">
         <v>1047.5971914594015</v>
       </c>
-      <c r="F33" s="76">
+      <c r="F37" s="70">
         <v>1047.5971914594015</v>
       </c>
-      <c r="G33">
+      <c r="G37">
         <v>1047.5971914594015</v>
       </c>
-      <c r="H33">
+      <c r="H37">
         <v>1047.5971914594015</v>
       </c>
     </row>
-    <row r="34" spans="1:8" s="63" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+    <row r="38" spans="1:8" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>48</v>
       </c>
-      <c r="E34" s="63">
+      <c r="E38" s="60">
         <v>25.03</v>
       </c>
     </row>
@@ -1722,863 +1847,863 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F1" s="57" t="s">
+      <c r="F1" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="55">
+      <c r="G1" s="52">
         <f>AVERAGE(G4:G23)</f>
         <v>0.87090304908582861</v>
       </c>
-      <c r="H1" s="60" t="s">
+      <c r="H1" s="57" t="s">
         <v>40</v>
       </c>
-      <c r="I1" s="56">
+      <c r="I1" s="53">
         <f>AVERAGE(I4:I23)</f>
         <v>23.143484979265143</v>
       </c>
-      <c r="J1" s="60" t="s">
+      <c r="J1" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="K1" s="56">
+      <c r="K1" s="53">
         <f>AVERAGE(K4:K23)</f>
         <v>715.92776441314822</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="39"/>
-      <c r="B2" s="40"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="58" t="s">
+    <row r="2" spans="1:13" s="40" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="36"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="48" t="s">
+      <c r="G2" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="H2" s="61" t="s">
+      <c r="H2" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="50" t="s">
+      <c r="I2" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="J2" s="61" t="s">
+      <c r="J2" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="50" t="s">
+      <c r="K2" s="47" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="44" t="s">
+    <row r="3" spans="1:13" s="40" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="45" t="s">
+      <c r="B3" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="46" t="s">
+      <c r="C3" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="47" t="s">
+      <c r="D3" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="47" t="s">
+      <c r="E3" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="59" t="s">
+      <c r="F3" s="56" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="49" t="s">
+      <c r="G3" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="H3" s="62" t="s">
+      <c r="H3" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="I3" s="51" t="s">
+      <c r="I3" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="62" t="s">
+      <c r="J3" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="K3" s="51" t="s">
+      <c r="K3" s="48" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="22">
+      <c r="A4" s="19">
         <v>3</v>
       </c>
-      <c r="B4" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="24">
+      <c r="B4" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="21">
         <v>0</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="22">
         <v>2458401.4085999997</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="23">
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="F4" s="25">
+      <c r="F4" s="22">
         <v>2458401.4106999999</v>
       </c>
-      <c r="G4" s="52">
+      <c r="G4" s="49">
         <f>ABS((F4-D4)/E4)</f>
         <v>0.65625004936009645</v>
       </c>
-      <c r="H4" s="25">
+      <c r="H4" s="22">
         <v>2458401.4182000002</v>
       </c>
-      <c r="I4" s="52">
+      <c r="I4" s="49">
         <f>ABS((H4-D4)/E4)</f>
         <v>3.0000001424923539</v>
       </c>
-      <c r="J4" s="25">
+      <c r="J4" s="22">
         <v>2458401.4120999998</v>
       </c>
-      <c r="K4" s="52">
+      <c r="K4" s="49">
         <f>ABS((J4-D4)/E4)</f>
         <v>1.0937500337604433</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="22">
+      <c r="A5" s="19">
         <v>6</v>
       </c>
-      <c r="B5" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="24">
+      <c r="B5" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="21">
         <v>1</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="22">
         <v>2458483.2110000001</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="23">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="22">
         <v>2458483.2118000002</v>
       </c>
-      <c r="G5" s="52">
+      <c r="G5" s="49">
         <f t="shared" ref="G5:G23" si="0">ABS((F5-D5)/E5)</f>
         <v>0.23529412882292974</v>
       </c>
-      <c r="H5" s="25">
+      <c r="H5" s="22">
         <v>2458483.2052000002</v>
       </c>
-      <c r="I5" s="52">
+      <c r="I5" s="49">
         <f t="shared" ref="I5:I23" si="1">ABS((H5-D5)/E5)</f>
         <v>1.705882331246839</v>
       </c>
-      <c r="J5" s="25">
+      <c r="J5" s="22">
         <v>2458482.8635</v>
       </c>
-      <c r="K5" s="52">
+      <c r="K5" s="49">
         <f t="shared" ref="K5:K23" si="2">ABS((J5-D5)/E5)</f>
         <v>102.20588239676813</v>
       </c>
       <c r="M5" s="8"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="22">
+      <c r="A6" s="19">
         <v>9</v>
       </c>
-      <c r="B6" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="24">
+      <c r="B6" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="21">
         <v>2</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="22">
         <v>2458565.0902</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="23">
         <v>3.2499999999999999E-3</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="22">
         <v>2458565.0959000001</v>
       </c>
-      <c r="G6" s="52">
+      <c r="G6" s="49">
         <f t="shared" si="0"/>
         <v>1.7538461834192276</v>
       </c>
-      <c r="H6" s="25">
+      <c r="H6" s="22">
         <v>2458565.0822999999</v>
       </c>
-      <c r="I6" s="52">
+      <c r="I6" s="49">
         <f t="shared" si="1"/>
         <v>2.4307692566743264</v>
       </c>
-      <c r="J6" s="25">
+      <c r="J6" s="22">
         <v>2458564.4419</v>
       </c>
-      <c r="K6" s="52">
+      <c r="K6" s="49">
         <f t="shared" si="2"/>
         <v>199.47692307715232</v>
       </c>
       <c r="M6" s="8"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="27">
+      <c r="A7" s="24">
         <v>12</v>
       </c>
-      <c r="B7" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="29">
+      <c r="B7" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="26">
         <v>3</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="27">
         <v>2458647.3328</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="28">
         <v>4.4000000000000003E-3</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="27">
         <v>2458647.3298999998</v>
       </c>
-      <c r="G7" s="53">
+      <c r="G7" s="50">
         <f t="shared" si="0"/>
         <v>0.6590909536250612</v>
       </c>
-      <c r="H7" s="30">
+      <c r="H7" s="27">
         <v>2458647.3202</v>
       </c>
-      <c r="I7" s="53">
+      <c r="I7" s="50">
         <f t="shared" si="1"/>
         <v>2.8636363673616536</v>
       </c>
-      <c r="J7" s="30">
+      <c r="J7" s="27">
         <v>2458646.4597</v>
       </c>
-      <c r="K7" s="53">
+      <c r="K7" s="50">
         <f t="shared" si="2"/>
         <v>198.43181817453691</v>
       </c>
       <c r="M7" s="8"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="22">
+      <c r="A8" s="19">
         <v>28</v>
       </c>
-      <c r="B8" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="24">
+      <c r="B8" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="21">
         <v>8</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="22">
         <v>2459065.2370000002</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="23">
         <v>2.3500000000000001E-3</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="22">
         <v>2459065.2407999998</v>
       </c>
-      <c r="G8" s="52">
+      <c r="G8" s="49">
         <f t="shared" si="0"/>
         <v>1.6170211057079598</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="22">
         <v>2459065.2357000001</v>
       </c>
-      <c r="I8" s="52">
+      <c r="I8" s="49">
         <f t="shared" si="1"/>
         <v>0.5531915404061053</v>
       </c>
-      <c r="J8" s="25">
+      <c r="J8" s="22">
         <v>2459064.2108999998</v>
       </c>
-      <c r="K8" s="52">
+      <c r="K8" s="49">
         <f t="shared" si="2"/>
         <v>436.63829802832703</v>
       </c>
       <c r="M8" s="8"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="22">
+      <c r="A9" s="19">
         <v>31</v>
       </c>
-      <c r="B9" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="24">
+      <c r="B9" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="21">
         <v>9</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="22">
         <v>2459148.4781999998</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="23">
         <v>2.65E-3</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="22">
         <v>2459148.4778999998</v>
       </c>
-      <c r="G9" s="52">
+      <c r="G9" s="49">
         <f t="shared" si="0"/>
         <v>0.11320753058172622</v>
       </c>
-      <c r="H9" s="25">
+      <c r="H9" s="22">
         <v>2459148.4284999999</v>
       </c>
-      <c r="I9" s="52">
+      <c r="I9" s="49">
         <f t="shared" si="1"/>
         <v>18.754716927431666</v>
       </c>
-      <c r="J9" s="25">
+      <c r="J9" s="22">
         <v>2459147.1962000001</v>
       </c>
-      <c r="K9" s="52">
+      <c r="K9" s="49">
         <f t="shared" si="2"/>
         <v>483.77358477632953</v>
       </c>
       <c r="M9" s="8"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="22">
+      <c r="A10" s="19">
         <v>34</v>
       </c>
-      <c r="B10" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="24">
-        <v>10</v>
-      </c>
-      <c r="D10" s="25">
+      <c r="B10" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="21">
+        <v>10</v>
+      </c>
+      <c r="D10" s="22">
         <v>2459231.1144000003</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="23">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="22">
         <v>2459231.1167000001</v>
       </c>
-      <c r="G10" s="52">
+      <c r="G10" s="49">
         <f t="shared" si="0"/>
         <v>1.0952380086694447</v>
       </c>
-      <c r="H10" s="25">
+      <c r="H10" s="22">
         <v>2459231.0216999999</v>
       </c>
-      <c r="I10" s="52">
+      <c r="I10" s="49">
         <f t="shared" si="1"/>
         <v>44.142857326992925</v>
       </c>
-      <c r="J10" s="25">
+      <c r="J10" s="22">
         <v>2459229.4999000002</v>
       </c>
-      <c r="K10" s="52">
+      <c r="K10" s="49">
         <f t="shared" si="2"/>
         <v>768.80952387693389</v>
       </c>
       <c r="M10" s="8"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="27">
+      <c r="A11" s="24">
         <v>37</v>
       </c>
-      <c r="B11" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="29">
+      <c r="B11" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="26">
         <v>11</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="27">
         <v>2459313.2535000001</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="28">
         <v>1.9E-3</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="27">
         <v>2459313.2577999998</v>
       </c>
-      <c r="G11" s="53">
+      <c r="G11" s="50">
         <f t="shared" si="0"/>
         <v>2.2631577265105749</v>
       </c>
-      <c r="H11" s="30">
+      <c r="H11" s="27">
         <v>2459313.1257000002</v>
       </c>
-      <c r="I11" s="53">
+      <c r="I11" s="50">
         <f t="shared" si="1"/>
         <v>67.263157842190637</v>
       </c>
-      <c r="J11" s="30">
+      <c r="J11" s="27">
         <v>2459311.2730999999</v>
       </c>
-      <c r="K11" s="53">
+      <c r="K11" s="50">
         <f t="shared" si="2"/>
         <v>1042.3157895964227</v>
       </c>
       <c r="M11" s="8"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="22">
+      <c r="A12" s="19">
         <v>61</v>
       </c>
-      <c r="B12" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="24">
+      <c r="B12" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="21">
         <v>19</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="22">
         <v>2459976.0493000001</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="23">
         <v>4.4000000000000003E-3</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="22">
         <v>2459976.0480999998</v>
       </c>
-      <c r="G12" s="52">
+      <c r="G12" s="49">
         <f t="shared" si="0"/>
         <v>0.27272733859717846</v>
       </c>
-      <c r="H12" s="25">
+      <c r="H12" s="22">
         <v>2459976.0643000002</v>
       </c>
-      <c r="I12" s="52">
+      <c r="I12" s="49">
         <f t="shared" si="1"/>
         <v>3.4090909387238999</v>
       </c>
-      <c r="J12" s="25">
+      <c r="J12" s="22">
         <v>2459973.1538</v>
       </c>
-      <c r="K12" s="52">
+      <c r="K12" s="49">
         <f t="shared" si="2"/>
         <v>658.06818184104156</v>
       </c>
       <c r="M12" s="8"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="22">
+      <c r="A13" s="19">
         <v>64</v>
       </c>
-      <c r="B13" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="32">
+      <c r="B13" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="29">
         <v>20</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="22">
         <v>2460059.6189000001</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="23">
         <v>2.3E-3</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="22">
         <v>2460059.6168</v>
       </c>
-      <c r="G13" s="52">
+      <c r="G13" s="49">
         <f t="shared" si="0"/>
         <v>0.91304354693578638</v>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="22">
         <v>2460059.5575000001</v>
       </c>
-      <c r="I13" s="52">
+      <c r="I13" s="49">
         <f t="shared" si="1"/>
         <v>26.695652176504549</v>
       </c>
-      <c r="J13" s="25">
+      <c r="J13" s="22">
         <v>2460056.5010000002</v>
       </c>
-      <c r="K13" s="52">
+      <c r="K13" s="49">
         <f t="shared" si="2"/>
         <v>1355.6086956320898</v>
       </c>
       <c r="M13" s="8"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="27">
+      <c r="A14" s="24">
         <v>67</v>
       </c>
-      <c r="B14" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="33">
+      <c r="B14" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="30">
         <v>21</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="27">
         <v>2460142.6048000003</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="28">
         <v>2.2499999999999998E-3</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="27">
         <v>2460142.6061</v>
       </c>
-      <c r="G14" s="53">
+      <c r="G14" s="50">
         <f t="shared" si="0"/>
         <v>0.57777762413024902</v>
       </c>
-      <c r="H14" s="30">
+      <c r="H14" s="27">
         <v>2460142.4610000001</v>
       </c>
-      <c r="I14" s="53">
+      <c r="I14" s="50">
         <f t="shared" si="1"/>
         <v>63.911111197537849</v>
       </c>
-      <c r="J14" s="30">
+      <c r="J14" s="27">
         <v>2460139.1642999998</v>
       </c>
-      <c r="K14" s="53">
+      <c r="K14" s="50">
         <f t="shared" si="2"/>
         <v>1529.1111113296615</v>
       </c>
       <c r="M14" s="8"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="22">
+      <c r="A15" s="19">
         <v>89</v>
       </c>
-      <c r="B15" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="32">
+      <c r="B15" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="29">
         <v>28</v>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="22">
         <v>2460718.6126000001</v>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="23">
         <v>4.5799999999999999E-3</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="22">
         <v>2460718.6072</v>
       </c>
-      <c r="G15" s="52">
+      <c r="G15" s="49">
         <f t="shared" si="0"/>
         <v>1.1790393318932129</v>
       </c>
-      <c r="H15" s="25">
+      <c r="H15" s="22">
         <v>2460718.6047</v>
       </c>
-      <c r="I15" s="52">
+      <c r="I15" s="49">
         <f t="shared" si="1"/>
         <v>1.72489084807676</v>
       </c>
-      <c r="J15" s="25">
+      <c r="J15" s="22">
         <v>2460713.7359000002</v>
       </c>
-      <c r="K15" s="52">
+      <c r="K15" s="49">
         <f t="shared" si="2"/>
         <v>1064.7816593681491</v>
       </c>
       <c r="M15" s="8"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="22">
+      <c r="A16" s="19">
         <v>95</v>
       </c>
-      <c r="B16" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="32">
+      <c r="B16" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="29">
         <v>30</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="22">
         <v>2460886.2719999999</v>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="23">
         <v>4.5799999999999999E-3</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="22">
         <v>2460886.2751000002</v>
       </c>
-      <c r="G16" s="52">
+      <c r="G16" s="49">
         <f t="shared" si="0"/>
         <v>0.67685596547272531</v>
       </c>
-      <c r="H16" s="25">
+      <c r="H16" s="22">
         <v>2460886.3358999998</v>
       </c>
-      <c r="I16" s="52">
+      <c r="I16" s="49">
         <f t="shared" si="1"/>
         <v>13.951965054602862</v>
       </c>
-      <c r="J16" s="25">
+      <c r="J16" s="22">
         <v>2460881.5249999999</v>
       </c>
-      <c r="K16" s="52">
+      <c r="K16" s="49">
         <f t="shared" si="2"/>
         <v>1036.4628820903763</v>
       </c>
       <c r="M16" s="8"/>
     </row>
     <row r="17" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="34">
+      <c r="A17" s="31">
         <v>97</v>
       </c>
-      <c r="B17" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="36">
+      <c r="B17" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="33">
         <v>31</v>
       </c>
-      <c r="D17" s="37">
+      <c r="D17" s="34">
         <v>2460970.0865000002</v>
       </c>
-      <c r="E17" s="38">
+      <c r="E17" s="35">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="F17" s="37">
+      <c r="F17" s="34">
         <v>2460970.0811999999</v>
       </c>
-      <c r="G17" s="54">
+      <c r="G17" s="51">
         <f t="shared" si="0"/>
         <v>0.88333338499069214</v>
       </c>
-      <c r="H17" s="37">
+      <c r="H17" s="34">
         <v>2460970.0865000002</v>
       </c>
-      <c r="I17" s="54">
+      <c r="I17" s="51">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J17" s="37">
+      <c r="J17" s="34">
         <v>2460965.2303999998</v>
       </c>
-      <c r="K17" s="54">
+      <c r="K17" s="51">
         <f t="shared" si="2"/>
         <v>809.35000007351243</v>
       </c>
       <c r="M17" s="8"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="22">
+      <c r="A18" s="19">
         <v>88</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="29">
         <v>0</v>
       </c>
-      <c r="D18" s="25">
+      <c r="D18" s="22">
         <v>2460695.5345999999</v>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="23">
         <v>4.5799999999999999E-3</v>
       </c>
-      <c r="F18" s="25">
+      <c r="F18" s="22">
         <v>2460695.5397999999</v>
       </c>
-      <c r="G18" s="52">
+      <c r="G18" s="49">
         <f t="shared" si="0"/>
         <v>1.1353711821301535</v>
       </c>
-      <c r="H18" s="25">
+      <c r="H18" s="22">
         <v>2460695.3920999998</v>
       </c>
-      <c r="I18" s="52">
+      <c r="I18" s="49">
         <f t="shared" si="1"/>
         <v>31.113537134171573</v>
       </c>
-      <c r="J18" s="25">
+      <c r="J18" s="22">
         <v>2460691.4147000001</v>
       </c>
-      <c r="K18" s="52">
+      <c r="K18" s="49">
         <f t="shared" si="2"/>
         <v>899.54148467597611</v>
       </c>
       <c r="M18" s="8"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="22">
+      <c r="A19" s="19">
         <v>89</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="32">
+      <c r="C19" s="29">
         <v>1</v>
       </c>
-      <c r="D19" s="25">
+      <c r="D19" s="22">
         <v>2460736.6348999999</v>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="23">
         <v>4.5799999999999999E-3</v>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="22">
         <v>2460736.6342000002</v>
       </c>
-      <c r="G19" s="52">
+      <c r="G19" s="49">
         <f t="shared" si="0"/>
         <v>0.1528383716615527</v>
       </c>
-      <c r="H19" s="25">
+      <c r="H19" s="22">
         <v>2460736.4485999998</v>
       </c>
-      <c r="I19" s="52">
+      <c r="I19" s="49">
         <f t="shared" si="1"/>
         <v>40.676855933588143</v>
       </c>
-      <c r="J19" s="25">
+      <c r="J19" s="22">
         <v>2460732.3349000001</v>
       </c>
-      <c r="K19" s="52">
+      <c r="K19" s="49">
         <f t="shared" si="2"/>
         <v>938.86462878029158</v>
       </c>
       <c r="M19" s="8"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="22">
+      <c r="A20" s="19">
         <v>94</v>
       </c>
-      <c r="B20" s="23" t="s">
+      <c r="B20" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="32">
+      <c r="C20" s="29">
         <v>4</v>
       </c>
-      <c r="D20" s="25">
+      <c r="D20" s="22">
         <v>2460859.2275</v>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="23">
         <v>4.5799999999999999E-3</v>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="22">
         <v>2460859.2245</v>
       </c>
-      <c r="G20" s="52">
+      <c r="G20" s="49">
         <f t="shared" si="0"/>
         <v>0.65502183975481054</v>
       </c>
-      <c r="H20" s="25">
+      <c r="H20" s="22">
         <v>2460858.9695000001</v>
       </c>
-      <c r="I20" s="52">
+      <c r="I20" s="49">
         <f t="shared" si="1"/>
         <v>56.331877710549854</v>
       </c>
-      <c r="J20" s="25">
+      <c r="J20" s="22">
         <v>2460854.4205</v>
       </c>
-      <c r="K20" s="52">
+      <c r="K20" s="49">
         <f t="shared" si="2"/>
         <v>1049.5633187837996</v>
       </c>
       <c r="M20" s="8"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="22">
+      <c r="A21" s="19">
         <v>95</v>
       </c>
-      <c r="B21" s="23" t="s">
+      <c r="B21" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="32">
+      <c r="C21" s="29">
         <v>5</v>
       </c>
-      <c r="D21" s="25">
+      <c r="D21" s="22">
         <v>2460900.06</v>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="23">
         <v>4.5799999999999999E-3</v>
       </c>
-      <c r="F21" s="25">
+      <c r="F21" s="22">
         <v>2460900.0610000002</v>
       </c>
-      <c r="G21" s="52">
+      <c r="G21" s="49">
         <f t="shared" si="0"/>
         <v>0.21834064714252688</v>
       </c>
-      <c r="H21" s="25">
+      <c r="H21" s="22">
         <v>2460899.8029999998</v>
       </c>
-      <c r="I21" s="52">
+      <c r="I21" s="49">
         <f t="shared" si="1"/>
         <v>56.113537165080096</v>
       </c>
-      <c r="J21" s="25">
+      <c r="J21" s="22">
         <v>2460895.1200999999</v>
       </c>
-      <c r="K21" s="52">
+      <c r="K21" s="49">
         <f t="shared" si="2"/>
         <v>1078.5807860510904</v>
       </c>
       <c r="M21" s="8"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="22">
+      <c r="A22" s="19">
         <v>97</v>
       </c>
-      <c r="B22" s="23" t="s">
+      <c r="B22" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="32">
+      <c r="C22" s="29">
         <v>6</v>
       </c>
-      <c r="D22" s="25">
+      <c r="D22" s="22">
         <v>2460940.8199999998</v>
       </c>
-      <c r="E22" s="26">
+      <c r="E22" s="23">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="F22" s="25">
+      <c r="F22" s="22">
         <v>2460940.8517</v>
       </c>
-      <c r="G22" s="52">
+      <c r="G22" s="49">
         <f t="shared" si="0"/>
         <v>0.96060606566342432</v>
       </c>
-      <c r="H22" s="25">
+      <c r="H22" s="22">
         <v>2460940.6022999999</v>
       </c>
-      <c r="I22" s="52">
+      <c r="I22" s="49">
         <f t="shared" si="1"/>
         <v>6.5969696945764795</v>
       </c>
-      <c r="J22" s="25">
+      <c r="J22" s="22">
         <v>2460935.7941999999</v>
       </c>
-      <c r="K22" s="52">
+      <c r="K22" s="49">
         <f t="shared" si="2"/>
         <v>152.29696969529894</v>
       </c>
       <c r="M22" s="8"/>
     </row>
     <row r="23" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="34">
+      <c r="A23" s="31">
         <v>97</v>
       </c>
-      <c r="B23" s="35" t="s">
+      <c r="B23" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="36">
+      <c r="C23" s="33">
         <v>7</v>
       </c>
-      <c r="D23" s="37">
+      <c r="D23" s="34">
         <f>2460981.71</f>
         <v>2460981.71</v>
       </c>
-      <c r="E23" s="38">
+      <c r="E23" s="35">
         <v>0.01</v>
       </c>
-      <c r="F23" s="37">
+      <c r="F23" s="34">
         <v>2460981.7239999999</v>
       </c>
-      <c r="G23" s="54">
+      <c r="G23" s="51">
         <f t="shared" si="0"/>
         <v>1.3999999966472387</v>
       </c>
-      <c r="H23" s="37">
+      <c r="H23" s="34">
         <v>2460981.4937</v>
       </c>
-      <c r="I23" s="54">
+      <c r="I23" s="51">
         <f t="shared" si="1"/>
         <v>21.629999997094274</v>
       </c>
-      <c r="J23" s="37">
+      <c r="J23" s="34">
         <v>2460976.5742000001</v>
       </c>
-      <c r="K23" s="54">
+      <c r="K23" s="51">
         <f t="shared" si="2"/>
         <v>513.57999998144805</v>
       </c>
@@ -2634,19 +2759,19 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="69" t="s">
+      <c r="C2" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="70">
+      <c r="D2" s="67">
         <v>0.88500000000000001</v>
       </c>
-      <c r="E2" s="70">
+      <c r="E2" s="67">
         <v>0.88500000000000001</v>
       </c>
     </row>
@@ -2660,10 +2785,10 @@
       <c r="C3" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="63">
+      <c r="D3" s="60">
         <v>2.1278000000000001</v>
       </c>
-      <c r="E3" s="63">
+      <c r="E3" s="60">
         <v>2.1511999999999998</v>
       </c>
     </row>
@@ -2674,10 +2799,10 @@
       <c r="B4" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="63">
+      <c r="D4" s="60">
         <v>0.24979999999999999</v>
       </c>
-      <c r="E4" s="64">
+      <c r="E4" s="61">
         <v>0.25019847194350425</v>
       </c>
     </row>
@@ -2691,10 +2816,10 @@
       <c r="C5" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="65">
+      <c r="D5" s="62">
         <v>91.1</v>
       </c>
-      <c r="E5" s="65">
+      <c r="E5" s="62">
         <v>88.763733999999999</v>
       </c>
     </row>
@@ -2708,10 +2833,10 @@
       <c r="C6" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="63">
+      <c r="D6" s="60">
         <v>41.787799999999997</v>
       </c>
-      <c r="E6" s="64">
+      <c r="E6" s="61">
         <v>41.781945999999998</v>
       </c>
     </row>
@@ -2725,10 +2850,10 @@
       <c r="C7" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="63">
+      <c r="D7" s="60">
         <v>0.24</v>
       </c>
-      <c r="E7" s="63">
+      <c r="E7" s="60">
         <v>0</v>
       </c>
     </row>
@@ -2742,10 +2867,10 @@
       <c r="C8" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="65">
+      <c r="D8" s="62">
         <v>275.8</v>
       </c>
-      <c r="E8" s="65">
+      <c r="E8" s="62">
         <v>276.76663869301791</v>
       </c>
     </row>
@@ -2759,10 +2884,10 @@
       <c r="C9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="66">
+      <c r="D9" s="63">
         <v>339.54</v>
       </c>
-      <c r="E9" s="66">
+      <c r="E9" s="63">
         <v>337.15902078899757</v>
       </c>
     </row>
@@ -2776,10 +2901,10 @@
       <c r="C10" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="63">
+      <c r="D10" s="60">
         <v>2.6315</v>
       </c>
-      <c r="E10" s="64">
+      <c r="E10" s="61">
         <v>2.63849</v>
       </c>
     </row>
@@ -2790,10 +2915,10 @@
       <c r="B11" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="63">
+      <c r="D11" s="60">
         <v>3.7699999999999997E-2</v>
       </c>
-      <c r="E11" s="64">
+      <c r="E11" s="61">
         <v>3.5024375561053193E-2</v>
       </c>
     </row>
@@ -2807,10 +2932,10 @@
       <c r="C12" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="63">
+      <c r="D12" s="60">
         <v>89.69</v>
       </c>
-      <c r="E12" s="65">
+      <c r="E12" s="62">
         <v>89.711567000000002</v>
       </c>
     </row>
@@ -2827,7 +2952,7 @@
       <c r="D13" s="6">
         <v>81.463099999999997</v>
       </c>
-      <c r="E13" s="63">
+      <c r="E13" s="60">
         <v>81.820097000000004</v>
       </c>
     </row>
@@ -2841,10 +2966,10 @@
       <c r="C14" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="63">
+      <c r="D14" s="60">
         <v>0.8</v>
       </c>
-      <c r="E14" s="63">
+      <c r="E14" s="60">
         <v>-2.016956</v>
       </c>
     </row>
@@ -2858,10 +2983,10 @@
       <c r="C15" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="67">
+      <c r="D15" s="64">
         <v>298.89</v>
       </c>
-      <c r="E15" s="65">
+      <c r="E15" s="62">
         <v>303.62478284868769</v>
       </c>
     </row>
@@ -2875,10 +3000,10 @@
       <c r="C16" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="68">
+      <c r="D16" s="65">
         <v>142.72</v>
       </c>
-      <c r="E16" s="66">
+      <c r="E16" s="63">
         <v>137.89365221593033</v>
       </c>
     </row>
